--- a/data-raw/datasets/antimicrobials.xlsx
+++ b/data-raw/datasets/antimicrobials.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>aminacyl,aminopar,aminosalyl,aminox,apacil,deapasil,entepas,gabbropas,granupas,helipidyl,hellipidyl,nemasol,nippas,osacyl,pamacyl,pamisyl,paramisan,paramycin,parasal,parasalicil,parasalindon,pasade,pasalon,pasara,pascorbic,pasdium,pasem,paser,pasmed,pasnal,pasnodia,pasolac,passodico,pharmakon,propasa,rezipas,salvis,sanipirol,sanipriol,sodiopas,spectrum</t>
+          <t>aminacyl,aminopar,aminosalyl,aminox,apacil,deapasil,entepas,gabbropas,granupas,helipidyl,hellipidyl,nemasol,nippas,osacyl,pamacyl,pamisyl,paramisan,paramycin,parasal,parasalicil,parasalindon,pasade,pasalon,pasara,pascorbic,pasdium,pasem,paser,pasmed,pasnal,pasnodia,pasolac,passodico,propasa,rezipas,salvis,sanipirol,sanipriol,sodiopas</t>
         </is>
       </c>
       <c r="J2">
@@ -727,7 +727,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>amikacillin,amikacina,amikacine,amikacinum,amikavet,amikin,amikozit,amukin,arikace,briclin,butirosins,kaminax,lukadin,mikavir,potentox,prestwick</t>
+          <t>amikacillin,amikacina,amikacine,amikacinum,amikavet,amikin,amikozit,amukin,arikace,briclin,butirosins,kaminax,lukadin,mikavir,potentox</t>
         </is>
       </c>
       <c r="J6" t="e">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>blenamax,blenoxane,bleocin,bleomicin,bleomicina,bleomycine,bleomycins,bleomycinum,blexane,nbleomycinamide</t>
+          <t>blenamax,blenoxane,bleocin,bleomicin,bleomicina,bleomycine,bleomycins,bleomycinum,blexane</t>
         </is>
       </c>
       <c r="J45" t="e">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>alenfral,alfacet,alfatil,ceclor,cefachlor,cefaclorum,cefeaclor,cephaclor,compound,distaclor,keflor,kefolor,kefral,keftab,keftid,lilly,lopac,panacef,panoral,raniclor</t>
+          <t>alenfral,alfacet,alfatil,ceclor,cefachlor,cefaclorum,cefeaclor,cephaclor,compound,distaclor,keflor,kefolor,kefral,keftab,keftid,lilly,panacef,panoral,raniclor</t>
         </is>
       </c>
       <c r="J56">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>exblifep</t>
         </is>
       </c>
       <c r="J75" t="e">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>amudane,delmofulvina,epigriseofulvin,fulcin,fulcine,fulvicin,fulvidex,fulvina,fulvinil,fulvistatin,fungivin,greosin,gresfeed,gricin,grifulin,grifulvin,grisactin,griscofulvin,grisefuline,griseo,griseofulviin,griseofulvina,griseofulvine,griseofulvinum,griseomix,griseostatin,grisetin,grisofulvin,grisovin,grisowen,grizeofulvin,grysio,guservin,lamoryl,likuden,likunden,murfulvin,poncyl,spiro,spirofulvin,xuanjing</t>
+          <t>amudane,delmofulvina,epigriseofulvin,fulcin,fulcine,fulvicin,fulvidex,fulvina,fulvinil,fulvistatin,fungivin,greosin,gresfeed,gricin,grifulin,grifulvin,grisactin,griscofulvin,grisefuline,griseo,griseofulviin,griseofulvina,griseofulvine,griseofulvinum,griseomix,griseostatin,grisetin,grisofulvin,grisovin,grisowen,grizeofulvin,grysio,guservin,lamoryl,likuden,likunden,murfulvin,poncyl,spirofulvin,xuanjing</t>
         </is>
       </c>
       <c r="J222">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>imipemide,imipenemum,imipenen,primaxin,recarbrio,tienam,tienamycin</t>
+          <t>imipemide,imipenemum,imipenen,primaxin,tienam,tienamycin</t>
         </is>
       </c>
       <c r="J229" t="e">
@@ -14581,7 +14581,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>recarbrio</t>
         </is>
       </c>
       <c r="J231" t="e">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>brizoral,ethanone,extina,fungarest,fungoral,ketaconazole,ketocanazole,ketoconazol,ketoconazolum,ketodan,ketoderm,ketoisdin,ketozole,kuric,levoketoconazole,nizoral,normocort,panfungol,piperazine,recorlev,sebazole,teryzolin,terzolin,tocris,xolegel</t>
+          <t>brizoral,ethanone,extina,fungarest,fungoral,ketaconazole,ketocanazole,ketoconazol,ketoconazolum,ketodan,ketoderm,ketoisdin,ketozole,kuric,levoketoconazole,nizoral,normocort,panfungol,piperazine,recorlev,sebazole,teryzolin,terzolin,xolegel</t>
         </is>
       </c>
       <c r="J243">
@@ -21653,7 +21653,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>penmalin,pentcillin,peperacillin,peracin,piperacilina,piperacillina,piperacilline,piperacillinhydrate,piperacillinum,pipercillin,pipracil,tazocin</t>
+          <t>penmalin,pentcillin,peperacillin,peracin,piperacilina,piperacillina,piperacilline,piperacillinhydrate,piperacillinum,pipercillin,pipracil</t>
         </is>
       </c>
       <c r="J346" t="e">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>piptazobactam,tazonam,zobactin,zosyn</t>
+          <t>piptazobactam,tazocin,tazonam,zobactin,zosyn</t>
         </is>
       </c>
       <c r="J348" t="e">
@@ -28163,7 +28163,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>exblifep,tazobactamsalt,tazobactamum,tazobactum</t>
+          <t>tazobactamsalt,tazobactamum,tazobactum</t>
         </is>
       </c>
       <c r="J451" t="e">
@@ -29397,7 +29397,7 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>alaninamide,bryamycin,gargon,pharmakon,prestwick,sporangiomycin,thiactin,tiostrepton</t>
+          <t>alaninamide,bryamycin,gargon,sporangiomycin,thiactin,tiostrepton</t>
         </is>
       </c>
       <c r="J471" t="e">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>ticar,ticarcilina,ticarcilline,ticarcillinum,timentin</t>
+          <t>ticar,ticarcilina,ticarcilline,ticarcillinum</t>
         </is>
       </c>
       <c r="J473" t="e">
@@ -29581,7 +29581,7 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>augpenin</t>
+          <t>augpenin,timentin</t>
         </is>
       </c>
       <c r="J474" t="e">
@@ -31455,7 +31455,7 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>nuzolvence,spiro,zoliflodacina,zoliflodacine</t>
+          <t>nuzolvence,zoliflodacina,zoliflodacine</t>
         </is>
       </c>
       <c r="J505" t="e">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>bleomycetin,boanmycin,nbleomycinamide,pingyangmycin</t>
+          <t>bleomycetin,boanmycin,pingyangmycin</t>
         </is>
       </c>
       <c r="J506" t="e">

--- a/data-raw/datasets/antimicrobials.xlsx
+++ b/data-raw/datasets/antimicrobials.xlsx
@@ -369,7 +369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:N506"/>
+  <dimension ref="A1:N507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1">
@@ -25701,25 +25701,25 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B412">
-        <v>20055036</v>
+          <t>SUD1</t>
+        </is>
+      </c>
+      <c r="B412" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Sulbenicillin</t>
+          <t>Sulbactam/durlobactam</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Penicillins,Beta-lactams</t>
+          <t>Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>J01CA16,QJ01CA16</t>
+          <t>J01CG30</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -25729,17 +25729,17 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Penicillins with extended spectrum</t>
+          <t>Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>sulben</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>kedacillin,kedacillina,sulbenicilina,sulbenicilline,sulbenicillinum,sulpelin</t>
+          <t>xacduro</t>
         </is>
       </c>
       <c r="J412" t="e">
@@ -25748,13 +25748,11 @@
       <c r="K412" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L412">
-        <v>15</v>
-      </c>
-      <c r="M412" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+      <c r="L412" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M412" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N412" t="inlineStr">
         <is>
@@ -25765,41 +25763,45 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>SUC</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B413">
-        <v>5318</v>
+        <v>20055036</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Sulconazole</t>
+          <t>Sulbenicillin</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Antifungals</t>
+          <t>Penicillins,Beta-lactams</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>D01AC09,QD01AC09</t>
-        </is>
-      </c>
-      <c r="F413" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G413" t="e">
-        <v>#N/A</v>
+          <t>J01CA16,QJ01CA16</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Beta-lactam antibacterials, penicillins</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Penicillins with extended spectrum</t>
+        </is>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>sulben</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
         <is>
-          <t>sulconazol,sulconazolum</t>
+          <t>kedacillin,kedacillina,sulbenicilina,sulbenicilline,sulbenicillinum,sulpelin</t>
         </is>
       </c>
       <c r="J413" t="e">
@@ -25808,11 +25810,13 @@
       <c r="K413" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L413" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M413" t="e">
-        <v>#N/A</v>
+      <c r="L413">
+        <v>15</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N413" t="inlineStr">
         <is>
@@ -25823,25 +25827,25 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>SUP</t>
+          <t>SUC</t>
         </is>
       </c>
       <c r="B414">
-        <v>6634</v>
+        <v>5318</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Sulfachlorpyridazine</t>
+          <t>Sulconazole</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Sulfonamides</t>
+          <t>Antifungals</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>QJ01EQ12</t>
+          <t>D01AC09,QD01AC09</t>
         </is>
       </c>
       <c r="F414" t="e">
@@ -25852,12 +25856,12 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>sulchl</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>cluricol,cosulid,cosumix,durasulf,nefrosul,nsulfanilamide,prinzone,solfaclorpiridazina,sonilyn,sulfacloropiridazina,sulfaclorpiridazina,vetisulid</t>
+          <t>sulconazol,sulconazolum</t>
         </is>
       </c>
       <c r="J414" t="e">
@@ -25881,54 +25885,48 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>SDI</t>
+          <t>SUP</t>
         </is>
       </c>
       <c r="B415">
-        <v>5215</v>
+        <v>6634</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Sulfadiazine</t>
+          <t>Sulfachlorpyridazine</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Trimethoprims,Sulfonamides</t>
+          <t>Sulfonamides</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>J01EC02,QJ01EQ10</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>Sulfonamides and trimethoprim</t>
-        </is>
-      </c>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>Intermediate-acting sulfonamides</t>
-        </is>
+          <t>QJ01EQ12</t>
+        </is>
+      </c>
+      <c r="F415" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G415" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>suldia</t>
+          <t>sulchl</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>codiazine,cremodiazine,cremotres,debenal,deltazina,dermazin,dermazine,diazolone,diazovit,eskadiazine,flamazine,geben,liquadiazine,microsulfon,neazine,neotrizine,palatrize,piridisir,pirimal,pyrimal,quadetts,quadramoid,sanodiazine,silbertone,sildaflo,silvadene,silvazine,silver,silveramide,sliverex,solfadiazina,spofadrizine,sterazine,sulfacombin,sulfadiazene,sulfadiazin,sulfadiazina,sulfadiazinum,sulfapirimidin,sulfapyrimidin,sulfapyrimidine,sulfatryl,sulfazine,sulfolex,sulfonsol,sulfose,sulphadiazine,terfonyl,theradiazine,thermazene,trifonamide,trisem,truozine</t>
-        </is>
-      </c>
-      <c r="J415">
-        <v>0.6</v>
-      </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>cluricol,cosulid,cosumix,durasulf,nefrosul,nsulfanilamide,prinzone,solfaclorpiridazina,sonilyn,sulfacloropiridazina,sulfaclorpiridazina,vetisulid</t>
+        </is>
+      </c>
+      <c r="J415" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K415" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L415" t="e">
         <v>#N/A</v>
@@ -25938,22 +25936,22 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>18984-5,27216-1,463-0,464-8,465-5,466-3,59742-7,6907-0,7050-8</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>SLT</t>
+          <t>SDI</t>
         </is>
       </c>
       <c r="B416">
-        <v>122284</v>
+        <v>5215</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Sulfadiazine/tetroxoprim</t>
+          <t>Sulfadiazine</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -25963,7 +25961,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>J01EE06</t>
+          <t>J01EC02,QJ01EQ10</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -25973,24 +25971,26 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+          <t>Intermediate-acting sulfonamides</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>suldia</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>berlocombin,cotetroxazine,potesept,trimerazine</t>
-        </is>
-      </c>
-      <c r="J416" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K416" t="e">
-        <v>#N/A</v>
+          <t>codiazine,cremodiazine,cremotres,debenal,deltazina,dermazin,dermazine,diazolone,diazovit,eskadiazine,flamazine,geben,liquadiazine,microsulfon,neazine,neotrizine,palatrize,piridisir,pirimal,pyrimal,quadetts,quadramoid,sanodiazine,silbertone,sildaflo,silvadene,silvazine,silver,silveramide,sliverex,solfadiazina,spofadrizine,sterazine,sulfacombin,sulfadiazene,sulfadiazin,sulfadiazina,sulfadiazinum,sulfapirimidin,sulfapyrimidin,sulfapyrimidine,sulfatryl,sulfazine,sulfolex,sulfonsol,sulfose,sulphadiazine,terfonyl,theradiazine,thermazene,trifonamide,trisem,truozine</t>
+        </is>
+      </c>
+      <c r="J416">
+        <v>0.6</v>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L416" t="e">
         <v>#N/A</v>
@@ -26000,22 +26000,22 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18984-5,27216-1,463-0,464-8,465-5,466-3,59742-7,6907-0,7050-8</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>SLT1</t>
+          <t>SLT</t>
         </is>
       </c>
       <c r="B417">
-        <v>64932</v>
+        <v>122284</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Sulfadiazine/trimethoprim</t>
+          <t>Sulfadiazine/tetroxoprim</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>J01EE02,QJ01EW10,QJ51RE01</t>
+          <t>J01EE06</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>antastmon,astra,ditrim,ditrivet,sultrisan,triglobe,trimin,tucoprim,uniprim</t>
+          <t>berlocombin,cotetroxazine,potesept,trimerazine</t>
         </is>
       </c>
       <c r="J417" t="e">
@@ -26069,15 +26069,15 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>SUD</t>
+          <t>SLT1</t>
         </is>
       </c>
       <c r="B418">
-        <v>5323</v>
+        <v>64932</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Sulfadimethoxine</t>
+          <t>Sulfadiazine/trimethoprim</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>J01ED01,QJ01EQ09,QP51BA01</t>
+          <t>J01EE02,QJ01EW10,QJ51RE01</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -26097,26 +26097,24 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Long-acting sulfonamides</t>
+          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>sdimet</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>abcid,agribon,albon,arnosulfan,bactotril,bactrovet,deposul,diasulfa,diasulfyl,dimetazina,dinosol,dorisul,fuxal,lasibon,madribon,madrigid,madriqid,madroxin,madroxine,maxulvet,mecozine,memcozine,metoxidon,neostrepal,neostreptal,nsulfanilamidesalt,omnibon,persulfen,radonin,redifal,rofenaid,roscosulf,scandisil,solfadimetossina,sudine,suldixine,sulfabon,sulfadimethoxin,sulfadimethoxinesalt,sulfadimethoxinum,sulfadimetossina,sulfadimetoxin,sulfadimetoxina,sulfadimetoxine,sulfadimoxine,sulfastop,sulfoplan,sulforal,sulphadimethoxine,sulxin,sumbio,symbio,theracanzan,ultrasulfon</t>
-        </is>
-      </c>
-      <c r="J418">
-        <v>0.5</v>
-      </c>
-      <c r="K418" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>antastmon,astra,ditrim,ditrivet,sultrisan,triglobe,trimin,tucoprim,uniprim</t>
+        </is>
+      </c>
+      <c r="J418" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K418" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L418" t="e">
         <v>#N/A</v>
@@ -26126,22 +26124,22 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>87799-3,87803-3</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>SDM</t>
+          <t>SUD</t>
         </is>
       </c>
       <c r="B419">
-        <v>5327</v>
+        <v>5323</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Sulfadimidine</t>
+          <t>Sulfadimethoxine</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -26151,7 +26149,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>J01EB03,QJ01EQ03,QP51AG01</t>
+          <t>J01ED01,QJ01EQ09,QP51BA01</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -26161,21 +26159,21 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Short-acting sulfonamides</t>
+          <t>Long-acting sulfonamides</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>suldim</t>
+          <t>sdimet</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>azolmetazin,bovibol,calfspan,cremomethazine,diazil,diazilsulfadine,diazyl,dimezathine,intradine,kelametazine,mermeth,neasina,neazina,panazin,pirmazin,primazin,solfadimidina,spanbolet,sulfadimerazine,sulfadimesin,sulfadimesine,sulfadimethyldiazine,sulfadimezin,sulfadimezine,sulfadimezinum,sulfadimidin,sulfadimidina,sulfadimidinum,sulfadimidinun,sulfadine,sulfametazina,sulfametazyny,sulfamethiazine,sulfamezathine,sulfamidine,sulfodimesin,sulfodimezine,sulmet,sulphadimidine,sulphamethasine,sulphamethazine,sulphamezathine,sulphamidine,sulphodimezine,superseptil,superseptyl,vertolan,vesadin</t>
+          <t>abcid,agribon,albon,arnosulfan,bactotril,bactrovet,deposul,diasulfa,diasulfyl,dimetazina,dinosol,dorisul,fuxal,lasibon,madribon,madrigid,madriqid,madroxin,madroxine,maxulvet,mecozine,memcozine,metoxidon,neostrepal,neostreptal,nsulfanilamidesalt,omnibon,persulfen,radonin,redifal,rofenaid,roscosulf,scandisil,solfadimetossina,sudine,suldixine,sulfabon,sulfadimethoxin,sulfadimethoxinesalt,sulfadimethoxinum,sulfadimetossina,sulfadimetoxin,sulfadimetoxina,sulfadimetoxine,sulfadimoxine,sulfastop,sulfoplan,sulforal,sulphadimethoxine,sulxin,sumbio,symbio,theracanzan,ultrasulfon</t>
         </is>
       </c>
       <c r="J419">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
@@ -26190,22 +26188,22 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>87799-3,87803-3</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>SLT2</t>
-        </is>
-      </c>
-      <c r="B420" t="e">
-        <v>#N/A</v>
+          <t>SDM</t>
+        </is>
+      </c>
+      <c r="B420">
+        <v>5327</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Sulfadimidine/trimethoprim</t>
+          <t>Sulfadimidine</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -26215,7 +26213,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>J01EE05,QJ01EW03</t>
+          <t>J01EB03,QJ01EQ03,QP51AG01</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -26225,24 +26223,26 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+          <t>Short-acting sulfonamides</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>suldim</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J420" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K420" t="e">
-        <v>#N/A</v>
+          <t>azolmetazin,bovibol,calfspan,cremomethazine,diazil,diazilsulfadine,diazyl,dimezathine,intradine,kelametazine,mermeth,neasina,neazina,panazin,pirmazin,primazin,solfadimidina,spanbolet,sulfadimerazine,sulfadimesin,sulfadimesine,sulfadimethyldiazine,sulfadimezin,sulfadimezine,sulfadimezinum,sulfadimidin,sulfadimidina,sulfadimidinum,sulfadimidinun,sulfadine,sulfametazina,sulfametazyny,sulfamethiazine,sulfamezathine,sulfamidine,sulfodimesin,sulfodimezine,sulmet,sulphadimidine,sulphamethasine,sulphamethazine,sulphamezathine,sulphamidine,sulphodimezine,superseptil,superseptyl,vertolan,vesadin</t>
+        </is>
+      </c>
+      <c r="J420">
+        <v>4</v>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L420" t="e">
         <v>#N/A</v>
@@ -26259,15 +26259,15 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="B421">
-        <v>5344</v>
+          <t>SLT2</t>
+        </is>
+      </c>
+      <c r="B421" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Sulfafurazole</t>
+          <t>Sulfadimidine/trimethoprim</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -26277,7 +26277,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>J01EB05,QJ01EQ05,QS01AB02,S01AB02</t>
+          <t>J01EE05,QJ01EW03</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -26287,34 +26287,30 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Short-acting sulfonamides</t>
+          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>sfsz</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>accuzole,alphazole,amidoxal,astrazolo,azosulfizin,bactesulf,barazae,chemouag,cosoxazole,dorsulfan,entusil,entusul,ganda,gantrisin,gantrisine,gantrisona,gantrizin,gantrosan,isoxamin,neazolin,neoxazol,novazolo,novosaxazole,nsulphanilamide,pancid,pediazole,renosulfan,resoxol,roxosul,roxoxol,saxosozine,sodizole,solfafurazolo,sosol,soxamide,soxisol,soxitabs,soxomide,stansin,sulbio,sulfafurazol,sulfafurazolum,sulfagan,sulfagen,sulfaisoxazole,sulfalar,sulfapolar,sulfasol,sulfasoxazole,sulfasoxizole,sulfazin,sulfisin,sulfisonazole,sulfisoxasole,sulfisoxazol,sulfisoxazolum,sulfizin,sulfizol,sulfizole,sulfofurazole,sulfoxol,suloxsol,sulphafuraz,sulphafurazol,sulphafurazole,sulphafurazolum,sulphaisoxazole,sulphisoxazol,sulphisoxazole,sulphofurazole,sulsoxin,thiasin,unisulf,urisoxin,uritrisin,urogan</t>
-        </is>
-      </c>
-      <c r="J421">
-        <v>4</v>
-      </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L421">
-        <v>4</v>
-      </c>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J421" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K421" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L421" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M421" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N421" t="inlineStr">
         <is>
@@ -26325,15 +26321,15 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>SLF1</t>
+          <t>SLF</t>
         </is>
       </c>
       <c r="B422">
-        <v>5343</v>
+        <v>5344</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Sulfaisodimidine</t>
+          <t>Sulfafurazole</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -26343,7 +26339,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>J01EB01</t>
+          <t>J01EB05,QJ01EQ05,QS01AB02,S01AB02</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -26358,12 +26354,12 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>sfsz</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>aristamid,aristamide,aristogyn,domain,domian,elcosin,elcosine,elkosil,elkosin,elkosine,erycon,isosulf,mefenal,solfisomidina,sulfadimetine,sulfaisodimerazine,sulfaisodimidinum,sulfaisomidine,sulfasomidine,sulfisomidin,sulfisomidina,sulfisomidine,sulfisomidinum,sulphasomidine</t>
+          <t>accuzole,alphazole,amidoxal,astrazolo,azosulfizin,bactesulf,barazae,chemouag,cosoxazole,dorsulfan,entusil,entusul,ganda,gantrisin,gantrisine,gantrisona,gantrizin,gantrosan,isoxamin,neazolin,neoxazol,novazolo,novosaxazole,nsulphanilamide,pancid,pediazole,renosulfan,resoxol,roxosul,roxoxol,saxosozine,sodizole,solfafurazolo,sosol,soxamide,soxisol,soxitabs,soxomide,stansin,sulbio,sulfafurazol,sulfafurazolum,sulfagan,sulfagen,sulfaisoxazole,sulfalar,sulfapolar,sulfasol,sulfasoxazole,sulfasoxizole,sulfazin,sulfisin,sulfisonazole,sulfisoxasole,sulfisoxazol,sulfisoxazolum,sulfizin,sulfizol,sulfizole,sulfofurazole,sulfoxol,suloxsol,sulphafuraz,sulphafurazol,sulphafurazole,sulphafurazolum,sulphaisoxazole,sulphisoxazol,sulphisoxazole,sulphofurazole,sulsoxin,thiasin,unisulf,urisoxin,uritrisin,urogan</t>
         </is>
       </c>
       <c r="J422">
@@ -26391,15 +26387,15 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>SLF2</t>
+          <t>SLF1</t>
         </is>
       </c>
       <c r="B423">
-        <v>9047</v>
+        <v>5343</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Sulfalene</t>
+          <t>Sulfaisodimidine</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -26409,7 +26405,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>J01ED02,QJ01EQ19</t>
+          <t>J01EB01</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -26419,7 +26415,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Long-acting sulfonamides</t>
+          <t>Short-acting sulfonamides</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -26429,22 +26425,24 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>dalysep,farmitalia,kelfizin,kelfizina,kelfizine,policydal,solfametopirazina,sulfalen,sulfaleno,sulfalenum,sulfamethopyrazine,sulfamethoxypyrazine,sulfametopyrazine,sulfametoxypyridazin,sulphalene,sulphametopyrazine,vetkelfizina</t>
+          <t>aristamid,aristamide,aristogyn,domain,domian,elcosin,elcosine,elkosil,elkosin,elkosine,erycon,isosulf,mefenal,solfisomidina,sulfadimetine,sulfaisodimerazine,sulfaisodimidinum,sulfaisomidine,sulfasomidine,sulfisomidin,sulfisomidina,sulfisomidine,sulfisomidinum,sulphasomidine</t>
         </is>
       </c>
       <c r="J423">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="L423" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M423" t="e">
-        <v>#N/A</v>
+      <c r="L423">
+        <v>4</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N423" t="inlineStr">
         <is>
@@ -26455,15 +26453,15 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>SZO</t>
+          <t>SLF2</t>
         </is>
       </c>
       <c r="B424">
-        <v>187764</v>
+        <v>9047</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Sulfamazone</t>
+          <t>Sulfalene</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -26473,7 +26471,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>J01ED09</t>
+          <t>J01ED02,QJ01EQ19</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -26493,11 +26491,11 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>sulfamazona,sulfamazonum,sulfenazone</t>
+          <t>dalysep,farmitalia,kelfizin,kelfizina,kelfizine,policydal,solfametopirazina,sulfalen,sulfaleno,sulfalenum,sulfamethopyrazine,sulfamethoxypyrazine,sulfametopyrazine,sulfametoxypyridazin,sulphalene,sulphametopyrazine,vetkelfizina</t>
         </is>
       </c>
       <c r="J424">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
@@ -26519,15 +26517,15 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>SLF3</t>
+          <t>SZO</t>
         </is>
       </c>
       <c r="B425">
-        <v>5325</v>
+        <v>187764</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Sulfamerazine</t>
+          <t>Sulfamazone</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -26537,7 +26535,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>D06BA06,J01ED07,QD06BA06,QJ01EQ17</t>
+          <t>J01ED09</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -26552,16 +26550,16 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>sulmet</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>cremomerazine,kelamerazine,mebacid,mesulfa,methylpyrimal,methylsulfazin,methylsulfazine,metilsulfadiazin,metilsulfazin,percoccide,pyralcid,romezin,septacil,septosyl,solfamerazina,solumedin,solumedine,sulfameradine,sulfamerazin,sulfamerazina,sulfamerazinum,sulfamethyldiazine,sulphamerazine,sumedine</t>
+          <t>sulfamazona,sulfamazonum,sulfenazone</t>
         </is>
       </c>
       <c r="J425">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
@@ -26583,15 +26581,15 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>SLT3</t>
-        </is>
-      </c>
-      <c r="B426" t="e">
-        <v>#N/A</v>
+          <t>SLF3</t>
+        </is>
+      </c>
+      <c r="B426">
+        <v>5325</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Sulfamerazine/trimethoprim</t>
+          <t>Sulfamerazine</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -26601,7 +26599,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>J01EE07,QJ01EW18</t>
+          <t>D06BA06,J01ED07,QD06BA06,QJ01EQ17</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -26611,24 +26609,26 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+          <t>Long-acting sulfonamides</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>sulmet</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J426" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K426" t="e">
-        <v>#N/A</v>
+          <t>cremomerazine,kelamerazine,mebacid,mesulfa,methylpyrimal,methylsulfazin,methylsulfazine,metilsulfadiazin,metilsulfazin,percoccide,pyralcid,romezin,septacil,septosyl,solfamerazina,solumedin,solumedine,sulfameradine,sulfamerazin,sulfamerazina,sulfamerazinum,sulfamethyldiazine,sulphamerazine,sumedine</t>
+        </is>
+      </c>
+      <c r="J426">
+        <v>3</v>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L426" t="e">
         <v>#N/A</v>
@@ -26645,7 +26645,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SLT3</t>
         </is>
       </c>
       <c r="B427" t="e">
@@ -26653,24 +26653,28 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Sulfamethazine</t>
+          <t>Sulfamerazine/trimethoprim</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Sulfonamides</t>
+          <t>Trimethoprims,Sulfonamides</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F427" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G427" t="e">
-        <v>#N/A</v>
+          <t>J01EE07,QJ01EW18</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Sulfonamides and trimethoprim</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+        </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
@@ -26696,61 +26700,55 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t>87592-2</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>SLF4</t>
-        </is>
-      </c>
-      <c r="B428">
-        <v>5328</v>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="B428" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Sulfamethizole</t>
+          <t>Sulfamethazine</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Trimethoprims,Sulfonamides</t>
+          <t>Sulfonamides</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>B05CA04,D06BA04,J01EB02,QB05CA04,QD06BA04,QJ01EQ02,QS01AB01,S01AB01</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>Sulfonamides and trimethoprim</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>Short-acting sulfonamides</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F428" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G428" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>sfmz</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>aethazolum,ayerlucil,berlophen,gliprotiazol,globucid,globucin,globuzid,glyprothiazol,glyprothiazole,glyprothiazolum,glyprothizolum,lucosil,microsul,proklar,renasul,rufol,salimol,sethadil,solfametizolo,solfetidolo,sulfaethidiole,sulfaethidol,sulfaethidole,sulfaethidolum,sulfaetidol,sulfamethizol,sulfamethizolum,sulfametizol,sulfapyelon,sulfstat,sulfurine,sulphaethidole,sulphamethizole,tardipyrine,tetracid,thidicur,thiosulfil,ultrasul,urocydal,urodiaton,urolucosil,urosulfin</t>
-        </is>
-      </c>
-      <c r="J428">
-        <v>4</v>
-      </c>
-      <c r="K428" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J428" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K428" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L428" t="e">
         <v>#N/A</v>
@@ -26760,22 +26758,22 @@
       </c>
       <c r="N428" t="inlineStr">
         <is>
-          <t>60175-7,60176-5,60177-3</t>
+          <t>87592-2</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>SMX</t>
+          <t>SLF4</t>
         </is>
       </c>
       <c r="B429">
-        <v>5329</v>
+        <v>5328</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Sulfamethoxazole</t>
+          <t>Sulfamethizole</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -26785,7 +26783,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>J01EC01,QJ01EQ11</t>
+          <t>B05CA04,D06BA04,J01EB02,QB05CA04,QD06BA04,QJ01EQ02,QS01AB01,S01AB01</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -26795,21 +26793,21 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Intermediate-acting sulfonamides</t>
+          <t>Short-acting sulfonamides</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>sfmx,sulf,sulfam</t>
+          <t>sfmz</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>septran,septrin,simsinomin,sinomin,solfametossazolo,sulfamethalazole,sulfamethoxazolum,sulfamethoxizole,sulfamethylisoxazole,sulfametoxazol,sulfiodizole,sulfisomezole,sulphisomezole,urobak</t>
+          <t>aethazolum,ayerlucil,berlophen,gliprotiazol,globucid,globucin,globuzid,glyprothiazol,glyprothiazole,glyprothiazolum,glyprothizolum,lucosil,microsul,proklar,renasul,rufol,salimol,sethadil,solfametizolo,solfetidolo,sulfaethidiole,sulfaethidol,sulfaethidole,sulfaethidolum,sulfaetidol,sulfamethizol,sulfamethizolum,sulfametizol,sulfapyelon,sulfstat,sulfurine,sulphaethidole,sulphamethizole,tardipyrine,tetracid,thidicur,thiosulfil,ultrasul,urocydal,urodiaton,urolucosil,urosulfin</t>
         </is>
       </c>
       <c r="J429">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K429" t="inlineStr">
         <is>
@@ -26824,22 +26822,22 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t>10342-4,11577-4,18985-2,25271-8,39772-9,467-1,468-9,469-7,470-5,59971-2,59972-0,60333-2,72674-5,80549-9,80974-9</t>
+          <t>60175-7,60176-5,60177-3</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>SLF5</t>
+          <t>SMX</t>
         </is>
       </c>
       <c r="B430">
-        <v>5330</v>
+        <v>5329</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Sulfamethoxypyridazine</t>
+          <t>Sulfamethoxazole</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26849,7 +26847,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>J01ED05,QJ01EQ15</t>
+          <t>J01EC01,QJ01EQ11</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -26859,21 +26857,21 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Long-acting sulfonamides</t>
+          <t>Intermediate-acting sulfonamides</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>sfmx,sulf,sulfam</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>altezol,cysul,davosin,depovernil,durox,kineks,kinex,kynex,lederkyn,lentac,lisulfen,longin,medicel,midicel,midikel,myasul,opinsul,paramid,petrisul,piridolo,quinoseptyl,retamid,retasulfin,retasulphine,slosul,spofadazine,succinylsulfathi,sulfalex,sulfapiridazin,sulfapyridazine,sulfdurazin,sulfozona,sultirene,vinces</t>
+          <t>septran,septrin,simsinomin,sinomin,solfametossazolo,sulfamethalazole,sulfamethoxazolum,sulfamethoxizole,sulfamethylisoxazole,sulfametoxazol,sulfiodizole,sulfisomezole,sulphisomezole,urobak</t>
         </is>
       </c>
       <c r="J430">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="K430" t="inlineStr">
         <is>
@@ -26888,22 +26886,22 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>10342-4,11577-4,18985-2,25271-8,39772-9,467-1,468-9,469-7,470-5,59971-2,59972-0,60333-2,72674-5,80549-9,80974-9</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>SLF6</t>
+          <t>SLF5</t>
         </is>
       </c>
       <c r="B431">
-        <v>19596</v>
+        <v>5330</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Sulfametomidine</t>
+          <t>Sulfamethoxypyridazine</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -26913,7 +26911,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>J01ED03</t>
+          <t>J01ED05,QJ01EQ15</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -26933,14 +26931,16 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>duroprocin,methofadin,methofazine,solfametomidina,sulfametomidin,sulfametomidina,sulfametomidinum,telemid</t>
-        </is>
-      </c>
-      <c r="J431" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K431" t="e">
-        <v>#N/A</v>
+          <t>altezol,cysul,davosin,depovernil,durox,kineks,kinex,kynex,lederkyn,lentac,lisulfen,longin,medicel,midicel,midikel,myasul,opinsul,paramid,petrisul,piridolo,quinoseptyl,retamid,retasulfin,retasulphine,slosul,spofadazine,succinylsulfathi,sulfalex,sulfapiridazin,sulfapyridazine,sulfdurazin,sulfozona,sultirene,vinces</t>
+        </is>
+      </c>
+      <c r="J431">
+        <v>0.5</v>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L431" t="e">
         <v>#N/A</v>
@@ -26957,15 +26957,15 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SLF7</t>
+          <t>SLF6</t>
         </is>
       </c>
       <c r="B432">
-        <v>5326</v>
+        <v>19596</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Sulfametoxydiazine</t>
+          <t>Sulfametomidine</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26975,7 +26975,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>J01ED04</t>
+          <t>J01ED03</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -26995,16 +26995,14 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>bayrena,berlicid,dairena,durenat,juvoxin,kinecid,kirocid,kiron,longasulf,methoxypyrimal,solfametossidiazina,sulfameter,sulfametersalt,sulfamethorine,sulfamethoxine,sulfamethoxydiazin,sulfamethoxydiazine,sulfamethoxydin,sulfamethoxydine,sulfametin,sulfametinum,sulfametorine,sulfametorinum,sulfametoxidiazina,sulfametoxidine,sulfametoxydiazinum,sulla,sulphameter,sulphamethoxydiazine,supramid,ultrax</t>
-        </is>
-      </c>
-      <c r="J432">
-        <v>0.5</v>
-      </c>
-      <c r="K432" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>duroprocin,methofadin,methofazine,solfametomidina,sulfametomidin,sulfametomidina,sulfametomidinum,telemid</t>
+        </is>
+      </c>
+      <c r="J432" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K432" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L432" t="e">
         <v>#N/A</v>
@@ -27021,15 +27019,15 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>SLT4</t>
-        </is>
-      </c>
-      <c r="B433" t="e">
-        <v>#N/A</v>
+          <t>SLF7</t>
+        </is>
+      </c>
+      <c r="B433">
+        <v>5326</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Sulfametrole/trimethoprim</t>
+          <t>Sulfametoxydiazine</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -27039,7 +27037,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>J01EE03</t>
+          <t>J01ED04</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -27049,24 +27047,26 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+          <t>Long-acting sulfonamides</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>trsm</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J433" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K433" t="e">
-        <v>#N/A</v>
+          <t>bayrena,berlicid,dairena,durenat,juvoxin,kinecid,kirocid,kiron,longasulf,methoxypyrimal,solfametossidiazina,sulfameter,sulfametersalt,sulfamethorine,sulfamethoxine,sulfamethoxydiazin,sulfamethoxydiazine,sulfamethoxydin,sulfamethoxydine,sulfametin,sulfametinum,sulfametorine,sulfametorinum,sulfametoxidiazina,sulfametoxidine,sulfametoxydiazinum,sulla,sulphameter,sulphamethoxydiazine,supramid,ultrax</t>
+        </is>
+      </c>
+      <c r="J433">
+        <v>0.5</v>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L433" t="e">
         <v>#N/A</v>
@@ -27083,15 +27083,15 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>SLF8</t>
-        </is>
-      </c>
-      <c r="B434">
-        <v>12894</v>
+          <t>SLT4</t>
+        </is>
+      </c>
+      <c r="B434" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Sulfamoxole</t>
+          <t>Sulfametrole/trimethoprim</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>J01EC03</t>
+          <t>J01EE03</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -27111,34 +27111,30 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Intermediate-acting sulfonamides</t>
+          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>trsm</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>enterocura,justamil,oxasulfa,solfaguanolo,solfamossolo,sulfadimethyloxazole,sulfaguanol,sulfaguanole,sulfaguanolum,sulfamoxol,sulfamoxolum,sulfano,sulfavigor,sulfmidil,sulfono,sulfune,sulfuno,sulphamoxole,tardamid,tardamide</t>
-        </is>
-      </c>
-      <c r="J434">
-        <v>1</v>
-      </c>
-      <c r="K434" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L434">
-        <v>1</v>
-      </c>
-      <c r="M434" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J434" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K434" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L434" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M434" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N434" t="inlineStr">
         <is>
@@ -27149,15 +27145,15 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>SLT5</t>
-        </is>
-      </c>
-      <c r="B435" t="e">
-        <v>#N/A</v>
+          <t>SLF8</t>
+        </is>
+      </c>
+      <c r="B435">
+        <v>12894</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Sulfamoxole/trimethoprim</t>
+          <t>Sulfamoxole</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -27167,7 +27163,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>J01EE04</t>
+          <t>J01EC03</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -27177,7 +27173,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+          <t>Intermediate-acting sulfonamides</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -27187,20 +27183,24 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J435" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K435" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L435" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M435" t="e">
-        <v>#N/A</v>
+          <t>enterocura,justamil,oxasulfa,solfaguanolo,solfamossolo,sulfadimethyloxazole,sulfaguanol,sulfaguanole,sulfaguanolum,sulfamoxol,sulfamoxolum,sulfano,sulfavigor,sulfmidil,sulfono,sulfune,sulfuno,sulphamoxole,tardamid,tardamide</t>
+        </is>
+      </c>
+      <c r="J435">
+        <v>1</v>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L435">
+        <v>1</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N435" t="inlineStr">
         <is>
@@ -27211,15 +27211,15 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>SLF9</t>
-        </is>
-      </c>
-      <c r="B436">
-        <v>5333</v>
+          <t>SLT5</t>
+        </is>
+      </c>
+      <c r="B436" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Sulfanilamide</t>
+          <t>Sulfamoxole/trimethoprim</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -27229,7 +27229,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>D06BA05,J01EB06,QD06BA05,QJ01EQ06</t>
+          <t>J01EE04</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -27239,7 +27239,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Short-acting sulfonamides</t>
+          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>albexan,albosal,ambeside,antistrept,astreptine,astrocid,bacteramid,bactesid,collomide,colsulanyde,copticide,deseptyl,dipron,ergaseptine,erysipan,estreptocida,exoseptoplix,fourneau,gerison,gombardol,hydroxysulfonamide,infepan,lusil,lysococcine,neococcyl,orgaseptine,prontalbin,prontylin,proseptal,proseptine,proseptol,pysococcine,sanamid,septanilam,septinal,septolix,septoplex,septoplix,solfanilamide,stramid,strepamide,strepsan,streptagol,streptamid,streptamin,streptasol,streptocid,streptocide,streptocidum,streptoclase,streptocom,streptopan,streptosil,streptozol,streptozone,streptrocide,sulfamidyl,sulfamine,sulfana,sulfanalone,sulfanidyl,sulfanil,sulfanilamida,sulfanilamidomethan,sulfanilamidum,sulfanimide,sulfocidin,sulfocidine,sulfonylamide,sulphanilamide,sulphanilamidum,sulphonamide,therapol,tolder</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J436" t="e">
@@ -27273,15 +27273,15 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SLF10</t>
+          <t>SLF9</t>
         </is>
       </c>
       <c r="B437">
-        <v>68933</v>
+        <v>5333</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Sulfaperin</t>
+          <t>Sulfanilamide</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -27291,7 +27291,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>J01ED06</t>
+          <t>D06BA05,J01EB06,QD06BA05,QJ01EQ06</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -27301,7 +27301,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Long-acting sulfonamides</t>
+          <t>Short-acting sulfonamides</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27311,16 +27311,14 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>anastaf,archisulfa,archisulpha,avissul,chemiopen,demosulfan,demosulphan,durisan,isosulfamerazine,isosulphamerazine,methylsulfadiazin,methylsulfadiazine,methylsulphadiazine,novosul,orosulfan,pallidin,retardon,risulfasens,sulfaperina,sulfaperine,sulfaperinum,sulfatreis,sulfopirimidine,sulpenta,sulphaperin,sulphaperina,sulphaperinum</t>
-        </is>
-      </c>
-      <c r="J437">
-        <v>0.5</v>
-      </c>
-      <c r="K437" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>albexan,albosal,ambeside,antistrept,astreptine,astrocid,bacteramid,bactesid,collomide,colsulanyde,copticide,deseptyl,dipron,ergaseptine,erysipan,estreptocida,exoseptoplix,fourneau,gerison,gombardol,hydroxysulfonamide,infepan,lusil,lysococcine,neococcyl,orgaseptine,prontalbin,prontylin,proseptal,proseptine,proseptol,pysococcine,sanamid,septanilam,septinal,septolix,septoplex,septoplix,solfanilamide,stramid,strepamide,strepsan,streptagol,streptamid,streptamin,streptasol,streptocid,streptocide,streptocidum,streptoclase,streptocom,streptopan,streptosil,streptozol,streptozone,streptrocide,sulfamidyl,sulfamine,sulfana,sulfanalone,sulfanidyl,sulfanil,sulfanilamida,sulfanilamidomethan,sulfanilamidum,sulfanimide,sulfocidin,sulfocidine,sulfonylamide,sulphanilamide,sulphanilamidum,sulphonamide,therapol,tolder</t>
+        </is>
+      </c>
+      <c r="J437" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K437" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L437" t="e">
         <v>#N/A</v>
@@ -27337,15 +27335,15 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>SLF11</t>
+          <t>SLF10</t>
         </is>
       </c>
       <c r="B438">
-        <v>5335</v>
+        <v>68933</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Sulfaphenazole</t>
+          <t>Sulfaperin</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -27355,7 +27353,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>J01ED08,QJ01EQ08</t>
+          <t>J01ED06</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -27375,11 +27373,11 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>depocid,depotsulfonamide,eftolon,firmazolo,inamil,isarol,merian,orisul,orisulf,paidazolo,phenylsulfapyrazole,plisulfan,raziosulfa,solfafenazolo,sulfabid,sulfafenazol,sulfafenazolo,sulfaphenazol,sulfaphenazolum,sulfaphenazon,sulfaphenylpipazol,sulfaphenylpyrazol,sulfaphenylpyrazole,sulfonylpyrazol,sulphaphenazole,sulphenazole</t>
+          <t>anastaf,archisulfa,archisulpha,avissul,chemiopen,demosulfan,demosulphan,durisan,isosulfamerazine,isosulphamerazine,methylsulfadiazin,methylsulfadiazine,methylsulphadiazine,novosul,orosulfan,pallidin,retardon,risulfasens,sulfaperina,sulfaperine,sulfaperinum,sulfatreis,sulfopirimidine,sulpenta,sulphaperin,sulphaperina,sulphaperinum</t>
         </is>
       </c>
       <c r="J438">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K438" t="inlineStr">
         <is>
@@ -27401,15 +27399,15 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>SLF12</t>
+          <t>SLF11</t>
         </is>
       </c>
       <c r="B439">
-        <v>5336</v>
+        <v>5335</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Sulfapyridine</t>
+          <t>Sulfaphenazole</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -27419,7 +27417,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>J01EB04,QJ01EQ04</t>
+          <t>J01ED08,QJ01EQ08</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -27429,7 +27427,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Short-acting sulfonamides</t>
+          <t>Long-acting sulfonamides</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27439,7 +27437,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>adiplon,coccoclase,dagenan,eubasin,eubasinum,haptocil,piridazol,plurazol,pyriamid,pyridazol,relbapiridina,ronin,septipulmon,solfapiridina,soludagenan,streptosilpyridine,sulfapiridina,sulfapyridin,sulfapyridinum,sulfidin,sulfidine,sulphapyridin,sulphapyridine,thioseptal,trianon</t>
+          <t>depocid,depotsulfonamide,eftolon,firmazolo,inamil,isarol,merian,orisul,orisulf,paidazolo,phenylsulfapyrazole,plisulfan,raziosulfa,solfafenazolo,sulfabid,sulfafenazol,sulfafenazolo,sulfaphenazol,sulfaphenazolum,sulfaphenazon,sulfaphenylpipazol,sulfaphenylpyrazol,sulfaphenylpyrazole,sulfonylpyrazol,sulphaphenazole,sulphenazole</t>
         </is>
       </c>
       <c r="J439">
@@ -27458,39 +27456,43 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>14075-6,55580-5</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>SLF12</t>
         </is>
       </c>
       <c r="B440">
-        <v>60582</v>
+        <v>5336</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Sulfasuccinamide</t>
+          <t>Sulfapyridine</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Sulfonamides</t>
+          <t>Trimethoprims,Sulfonamides</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F440" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G440" t="e">
-        <v>#N/A</v>
+          <t>J01EB04,QJ01EQ04</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Sulfonamides and trimethoprim</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Short-acting sulfonamides</t>
+        </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
@@ -27499,14 +27501,16 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>sulfasuccinamid,sulfasuccinamida,sulfasuccinamidum</t>
-        </is>
-      </c>
-      <c r="J440" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K440" t="e">
-        <v>#N/A</v>
+          <t>adiplon,coccoclase,dagenan,eubasin,eubasinum,haptocil,piridazol,plurazol,pyriamid,pyridazol,relbapiridina,ronin,septipulmon,solfapiridina,soludagenan,streptosilpyridine,sulfapiridina,sulfapyridin,sulfapyridinum,sulfidin,sulfidine,sulphapyridin,sulphapyridine,thioseptal,trianon</t>
+        </is>
+      </c>
+      <c r="J440">
+        <v>1</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L440" t="e">
         <v>#N/A</v>
@@ -27516,52 +27520,48 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14075-6,55580-5</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SUT</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B441">
-        <v>5340</v>
+        <v>60582</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Sulfathiazole</t>
+          <t>Sulfasuccinamide</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Trimethoprims,Sulfonamides</t>
+          <t>Sulfonamides</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>D06BA02,J01EB07,QD06BA02,QJ01EQ07</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>Sulfonamides and trimethoprim</t>
-        </is>
-      </c>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>Short-acting sulfonamides</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F441" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G441" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>sulthi</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>azoquimiol,azoseptale,cerazol,cerazole,chemosept,cibazol,duatok,dulana,eleudron,enterobiocine,estafilol,formosulfathiazole,neostrepsan,norsulfasol,norsulfazol,norsulfazole,norsulfazolum,planomide,poliseptil,sanotiazol,septozol,solfatiazolo,soluthiazomide,streptosilthiazole,sulfamul,sulfaplex,sulfathiazol,sulfathiazolesalt,sulfathiazolum,sulfatiazol,sulfavitina,sulfocerol,sulphathiazole,sulzol,thiacoccine,thiasulfol,thiazamide,thiozamide,wintrazole</t>
+          <t>sulfasuccinamid,sulfasuccinamida,sulfasuccinamidum</t>
         </is>
       </c>
       <c r="J441" t="e">
@@ -27578,22 +27578,22 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>87591-4,87796-9,87797-7</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>SLF13</t>
+          <t>SUT</t>
         </is>
       </c>
       <c r="B442">
-        <v>3000579</v>
+        <v>5340</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Sulfathiourea</t>
+          <t>Sulfathiazole</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -27603,7 +27603,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>J01EB08</t>
+          <t>D06BA02,J01EB07,QD06BA02,QJ01EQ07</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -27618,21 +27618,19 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>sulthi</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>badional,baldinol,fontamide,salvoseptyl,solfatiourea,solufontamide,sulfanilthiourea,sulfathiocarbamid,sulfathiocarbamide,sulfathiocarbamidum,sulfathioureasalt,sulfathiouree,sulfatiourea,sulphathiourea</t>
-        </is>
-      </c>
-      <c r="J442">
-        <v>6</v>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>azoquimiol,azoseptale,cerazol,cerazole,chemosept,cibazol,duatok,dulana,eleudron,enterobiocine,estafilol,formosulfathiazole,neostrepsan,norsulfasol,norsulfazol,norsulfazole,norsulfazolum,planomide,poliseptil,sanotiazol,septozol,solfatiazolo,soluthiazomide,streptosilthiazole,sulfamul,sulfaplex,sulfathiazol,sulfathiazolesalt,sulfathiazolum,sulfatiazol,sulfavitina,sulfocerol,sulphathiazole,sulzol,thiacoccine,thiasulfol,thiazamide,thiozamide,wintrazole</t>
+        </is>
+      </c>
+      <c r="J442" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K442" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L442" t="e">
         <v>#N/A</v>
@@ -27642,55 +27640,61 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>87591-4,87796-9,87797-7</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>SOX</t>
-        </is>
-      </c>
-      <c r="B443" t="e">
-        <v>#N/A</v>
+          <t>SLF13</t>
+        </is>
+      </c>
+      <c r="B443">
+        <v>3000579</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Sulfisoxazole</t>
+          <t>Sulfathiourea</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Sulfonamides</t>
+          <t>Trimethoprims,Sulfonamides</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F443" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G443" t="e">
-        <v>#N/A</v>
+          <t>J01EB08</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Sulfonamides and trimethoprim</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Short-acting sulfonamides</t>
+        </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>sulfiz</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J443" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K443" t="e">
-        <v>#N/A</v>
+          <t>badional,baldinol,fontamide,salvoseptyl,solfatiourea,solufontamide,sulfanilthiourea,sulfathiocarbamid,sulfathiocarbamide,sulfathiocarbamidum,sulfathioureasalt,sulfathiouree,sulfatiourea,sulphathiourea</t>
+        </is>
+      </c>
+      <c r="J443">
+        <v>6</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L443" t="e">
         <v>#N/A</v>
@@ -27700,22 +27704,22 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>11578-2,18986-0,25226-2,471-3,472-1,473-9,474-7,9701-4</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>SSS</t>
-        </is>
-      </c>
-      <c r="B444">
-        <v>86225</v>
+          <t>SOX</t>
+        </is>
+      </c>
+      <c r="B444" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Sulfonamide</t>
+          <t>Sulfisoxazole</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -27736,7 +27740,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>sfna,sulami</t>
+          <t>sulfiz</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27758,27 +27762,27 @@
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>17674-3,17675-0,18987-8,35842-4,4040-2,4041-0,4042-8,475-4,476-2,477-0,478-8,75650-2</t>
+          <t>11578-2,18986-0,25226-2,471-3,472-1,473-9,474-7,9701-4</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>SLP</t>
+          <t>SSS</t>
         </is>
       </c>
       <c r="B445">
-        <v>9950244</v>
+        <v>86225</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Sulopenem</t>
+          <t>Sulfonamide</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sulfonamides</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -27794,12 +27798,12 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>sulope</t>
+          <t>sfna,sulami</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>orlynvah</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J445" t="e">
@@ -27816,61 +27820,55 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>55289-3,55290-1,55291-9</t>
+          <t>17674-3,17675-0,18987-8,35842-4,4040-2,4041-0,4042-8,475-4,476-2,477-0,478-8,75650-2</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>SLT6</t>
+          <t>SLP</t>
         </is>
       </c>
       <c r="B446">
-        <v>444022</v>
+        <v>9950244</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Sultamicillin</t>
+          <t>Sulopenem</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Penicillins,Beta-lactams,Beta-lactamase inhibitors</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>J01CR04,QJ01CR04</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>Beta-lactam antibacterials, penicillins</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>Combinations of penicillins, incl. beta-lactamase inhibitors</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F446" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G446" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>sultos</t>
+          <t>sulope</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>combisid,sultamicilina,sultamicilline,sultamicillinum,unacid</t>
-        </is>
-      </c>
-      <c r="J446">
-        <v>1.5</v>
-      </c>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>orlynvah</t>
+        </is>
+      </c>
+      <c r="J446" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K446" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L446" t="e">
         <v>#N/A</v>
@@ -27880,55 +27878,61 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>55289-3,55290-1,55291-9</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>SLT6</t>
         </is>
       </c>
       <c r="B447">
-        <v>46700778</v>
+        <v>444022</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Surotomycin</t>
+          <t>Sultamicillin</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Penicillins,Beta-lactams,Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F447" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G447" t="e">
-        <v>#N/A</v>
+          <t>J01CR04,QJ01CR04</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Beta-lactam antibacterials, penicillins</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Combinations of penicillins, incl. beta-lactamase inhibitors</t>
+        </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>sultos</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>surotomicina,surotomycine</t>
-        </is>
-      </c>
-      <c r="J447" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K447" t="e">
-        <v>#N/A</v>
+          <t>combisid,sultamicilina,sultamicilline,sultamicillinum,unacid</t>
+        </is>
+      </c>
+      <c r="J447">
+        <v>1.5</v>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L447" t="e">
         <v>#N/A</v>
@@ -27945,36 +27949,32 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B448">
-        <v>71447</v>
+        <v>46700778</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Talampicillin</t>
+          <t>Surotomycin</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Penicillins,Beta-lactams</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>J01CA15,QJ01CA15</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>Beta-lactam antibacterials, penicillins</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>Penicillins with extended spectrum</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F448" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G448" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
@@ -27983,16 +27983,14 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>aseocillin,phthalidyl,talampicilina,talampicilline,talampicillinum,talpen,yamacillin</t>
-        </is>
-      </c>
-      <c r="J448">
-        <v>2</v>
-      </c>
-      <c r="K448" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>surotomicina,surotomycine</t>
+        </is>
+      </c>
+      <c r="J448" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K448" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L448" t="e">
         <v>#N/A</v>
@@ -28002,39 +28000,43 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>18988-6,479-6,480-4,481-2,482-0</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>TLP</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="B449">
-        <v>163307</v>
+        <v>71447</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Talmetoprim</t>
+          <t>Talampicillin</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Penicillins,Beta-lactams</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F449" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G449" t="e">
-        <v>#N/A</v>
+          <t>J01CA15,QJ01CA15</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Beta-lactam antibacterials, penicillins</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Penicillins with extended spectrum</t>
+        </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
@@ -28043,14 +28045,16 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J449" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K449" t="e">
-        <v>#N/A</v>
+          <t>aseocillin,phthalidyl,talampicilina,talampicilline,talampicillinum,talpen,yamacillin</t>
+        </is>
+      </c>
+      <c r="J449">
+        <v>2</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L449" t="e">
         <v>#N/A</v>
@@ -28060,27 +28064,27 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18988-6,479-6,480-4,481-2,482-0</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>TAN</t>
+          <t>TLP</t>
         </is>
       </c>
       <c r="B450">
-        <v>76902493</v>
+        <v>163307</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Taniborbactam</t>
+          <t>Talmetoprim</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Carbapenems,Beta-lactams,Beta-lactamase inhibitors</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -28096,7 +28100,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>vnrx-5133</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -28125,45 +28129,41 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>TAZ</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="B451">
-        <v>123630</v>
+        <v>76902493</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Tazobactam</t>
+          <t>Taniborbactam</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Beta-lactamase inhibitors</t>
+          <t>Carbapenems,Beta-lactams,Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>J01CG02,QJ01CG02</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>Beta-lactam antibacterials, penicillins</t>
-        </is>
-      </c>
-      <c r="G451" t="inlineStr">
-        <is>
-          <t>Beta-lactamase inhibitors</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F451" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G451" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>tazo,tazoba</t>
+          <t>vnrx-5133</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>tazobactamsalt,tazobactamum,tazobactum</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J451" t="e">
@@ -28180,48 +28180,52 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>41719-6,41720-4,41721-2,41740-2</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>TBP</t>
+          <t>TAZ</t>
         </is>
       </c>
       <c r="B452">
-        <v>9800194</v>
+        <v>123630</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Tebipenem</t>
+          <t>Tazobactam</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Carbapenems,Beta-lactams</t>
+          <t>Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F452" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G452" t="e">
-        <v>#N/A</v>
+          <t>J01CG02,QJ01CG02</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Beta-lactam antibacterials, penicillins</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Beta-lactamase inhibitors</t>
+        </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tazo,tazoba</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tazobactamsalt,tazobactamum,tazobactum</t>
         </is>
       </c>
       <c r="J452" t="e">
@@ -28238,98 +28242,90 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>41719-6,41720-4,41721-2,41740-2</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TZD</t>
+          <t>TBP</t>
         </is>
       </c>
       <c r="B453">
-        <v>11234049</v>
+        <v>9800194</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Tedizolid</t>
+          <t>Tebipenem</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Oxazolidinones</t>
+          <t>Carbapenems,Beta-lactams</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>J01XX11,QJ01XX11</t>
-        </is>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
-      </c>
-      <c r="G453" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F453" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G453" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>tedi</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>torezolid</t>
-        </is>
-      </c>
-      <c r="J453">
-        <v>0.2</v>
-      </c>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L453">
-        <v>0.2</v>
-      </c>
-      <c r="M453" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J453" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K453" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L453" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M453" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>73586-0,73608-2,73631-4</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>TEC</t>
+          <t>TZD</t>
         </is>
       </c>
       <c r="B454">
-        <v>16131923</v>
+        <v>11234049</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Teicoplanin</t>
+          <t>Tedizolid</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Glycopeptides,Peptides</t>
+          <t>Oxazolidinones</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>J01XA02,QJ01XA02</t>
+          <t>J01XX11,QJ01XX11</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -28339,27 +28335,29 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Glycopeptide antibacterials</t>
+          <t>Other antibacterials</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>tec,tei,teic,teicop,tp,tpl,tpn</t>
+          <t>tedi</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J454" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K454" t="e">
-        <v>#N/A</v>
+          <t>torezolid</t>
+        </is>
+      </c>
+      <c r="J454">
+        <v>0.2</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L454">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
@@ -28368,22 +28366,22 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>18989-4,25534-9,25535-6,34378-0,34379-8,4043-6,483-8,484-6,485-3,486-1,7051-6,80968-1</t>
+          <t>73586-0,73608-2,73631-4</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TCM</t>
-        </is>
-      </c>
-      <c r="B455" t="e">
-        <v>#N/A</v>
+          <t>TEC</t>
+        </is>
+      </c>
+      <c r="B455">
+        <v>16131923</v>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Teicoplanin-macromethod</t>
+          <t>Teicoplanin</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -28393,18 +28391,22 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F455" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G455" t="e">
-        <v>#N/A</v>
+          <t>J01XA02,QJ01XA02</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Other antibacterials</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Glycopeptide antibacterials</t>
+        </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tec,tei,teic,teicop,tp,tpl,tpn</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28418,60 +28420,58 @@
       <c r="K455" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L455" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M455" t="e">
-        <v>#N/A</v>
+      <c r="L455">
+        <v>0.4</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18989-4,25534-9,25535-6,34378-0,34379-8,4043-6,483-8,484-6,485-3,486-1,7051-6,80968-1</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TLV</t>
-        </is>
-      </c>
-      <c r="B456">
-        <v>3081362</v>
+          <t>TCM</t>
+        </is>
+      </c>
+      <c r="B456" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Telavancin</t>
+          <t>Teicoplanin-macromethod</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Lipoglycopeptides,Glycopeptides,Peptides</t>
+          <t>Glycopeptides,Peptides</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>J01XA03,QJ01XA03</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
-      </c>
-      <c r="G456" t="inlineStr">
-        <is>
-          <t>Glycopeptide antibacterials</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F456" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G456" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>tela,telava</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>arbelic,nvancomycin,televancin</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J456" t="e">
@@ -28488,61 +28488,59 @@
       </c>
       <c r="N456" t="inlineStr">
         <is>
-          <t>72894-9,73630-6,85051-1,88886-7</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B457">
-        <v>3002190</v>
+        <v>3081362</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Telithromycin</t>
+          <t>Telavancin</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Lipoglycopeptides,Glycopeptides,Peptides</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>J01FA15,QJ01FA15</t>
+          <t>J01XA03,QJ01XA03</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>Macrolides, lincosamides and streptogramins</t>
+          <t>Other antibacterials</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Glycopeptide antibacterials</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>teli,telith</t>
+          <t>tela,telava</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>ketek,levviax</t>
-        </is>
-      </c>
-      <c r="J457">
-        <v>0.8</v>
-      </c>
-      <c r="K457" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>arbelic,nvancomycin,televancin</t>
+        </is>
+      </c>
+      <c r="J457" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K457" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L457" t="e">
         <v>#N/A</v>
@@ -28552,52 +28550,52 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t>35843-2,35844-0,35845-7,41722-0</t>
+          <t>72894-9,73630-6,85051-1,88886-7</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>TMX</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="B458">
-        <v>60021</v>
+        <v>3002190</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Temafloxacin</t>
+          <t>Telithromycin</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Fluoroquinolones,Quinolones</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>J01MA05,QJ01MA05</t>
+          <t>J01FA15,QJ01FA15</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Quinolone antibacterials</t>
+          <t>Macrolides, lincosamides and streptogramins</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>tema,temafl</t>
+          <t>teli,telith</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>omniflox,temafloxacina,temafloxacine,temafloxacino,temafloxacinum</t>
+          <t>ketek,levviax</t>
         </is>
       </c>
       <c r="J458">
@@ -28616,150 +28614,150 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t>18990-2,487-9,488-7,489-5,490-3</t>
+          <t>35843-2,35844-0,35845-7,41722-0</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>TMX</t>
         </is>
       </c>
       <c r="B459">
-        <v>171758</v>
+        <v>60021</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Temocillin</t>
+          <t>Temafloxacin</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Penicillins,Beta-lactams</t>
+          <t>Fluoroquinolones,Quinolones</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>J01CA17,QJ01CA17</t>
+          <t>J01MA05,QJ01MA05</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Beta-lactam antibacterials, penicillins</t>
+          <t>Quinolone antibacterials</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Penicillins with extended spectrum</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>temo,temoci</t>
+          <t>tema,temafl</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>negaban,temocilina,temocillina,temocilline,temocillinum</t>
-        </is>
-      </c>
-      <c r="J459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K459" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L459">
-        <v>4</v>
-      </c>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>omniflox,temafloxacina,temafloxacine,temafloxacino,temafloxacinum</t>
+        </is>
+      </c>
+      <c r="J459">
+        <v>0.8</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L459" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M459" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t>18991-0,491-1,492-9,493-7,494-5,54190-4</t>
+          <t>18990-2,487-9,488-7,489-5,490-3</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TRB</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="B460">
-        <v>1549008</v>
+        <v>171758</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Terbinafine</t>
+          <t>Temocillin</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Antifungals</t>
+          <t>Penicillins,Beta-lactams</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>D01AE15,D01BA02,QD01AE15,QD01BA02</t>
+          <t>J01CA17,QJ01CA17</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>Antifungals for systemic use</t>
+          <t>Beta-lactam antibacterials, penicillins</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>Antifungals for systemic use</t>
+          <t>Penicillins with extended spectrum</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>terb</t>
+          <t>temo,temoci</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>afogan,bramazil,bramizil,corbinal,lamasil,lamisil,muzonal,shoprite,terbina,terbinafina,terbinafinum,terbine,terbinex,terbisil,zabel</t>
-        </is>
-      </c>
-      <c r="J460">
-        <v>0.25</v>
-      </c>
-      <c r="K460" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L460" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M460" t="e">
-        <v>#N/A</v>
+          <t>negaban,temocilina,temocillina,temocilline,temocillinum</t>
+        </is>
+      </c>
+      <c r="J460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K460" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L460">
+        <v>4</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N460" t="inlineStr">
         <is>
-          <t>10720-1,10721-9,18992-8</t>
+          <t>18991-0,491-1,492-9,493-7,494-5,54190-4</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>TRB</t>
         </is>
       </c>
       <c r="B461">
-        <v>441383</v>
+        <v>1549008</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Terconazole</t>
+          <t>Terbinafine</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -28769,30 +28767,36 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>G01AG02,QG01AG02</t>
-        </is>
-      </c>
-      <c r="F461" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G461" t="e">
-        <v>#N/A</v>
+          <t>D01AE15,D01BA02,QD01AE15,QD01BA02</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Antifungals for systemic use</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Antifungals for systemic use</t>
+        </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>terb</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>fungistat,panlomyc,terazol,terconazol,terconazolum,tercospor,tetrazol,triaconazole,zazole</t>
-        </is>
-      </c>
-      <c r="J461" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K461" t="e">
-        <v>#N/A</v>
+          <t>afogan,bramazil,bramizil,corbinal,lamasil,lamisil,muzonal,shoprite,terbina,terbinafina,terbinafinum,terbine,terbinex,terbisil,zabel</t>
+        </is>
+      </c>
+      <c r="J461">
+        <v>0.25</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L461" t="e">
         <v>#N/A</v>
@@ -28802,43 +28806,39 @@
       </c>
       <c r="N461" t="inlineStr">
         <is>
-          <t>55196-0</t>
+          <t>10720-1,10721-9,18992-8</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>TRZ</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="B462">
-        <v>65720</v>
+        <v>441383</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Terizidone</t>
+          <t>Terconazole</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Antimycobacterials</t>
+          <t>Antifungals</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>J04AK03,QJ04AK03</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>Drugs for treatment of tuberculosis</t>
-        </is>
-      </c>
-      <c r="G462" t="inlineStr">
-        <is>
-          <t>Other drugs for treatment of tuberculosis</t>
-        </is>
+          <t>G01AG02,QG01AG02</t>
+        </is>
+      </c>
+      <c r="F462" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G462" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
@@ -28847,7 +28847,7 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>terivalidin,terizidona,terizidonum</t>
+          <t>fungistat,panlomyc,terazol,terconazol,terconazolum,tercospor,tetrazol,triaconazole,zazole</t>
         </is>
       </c>
       <c r="J462" t="e">
@@ -28864,88 +28864,84 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>55196-0</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>TCY</t>
+          <t>TRZ</t>
         </is>
       </c>
       <c r="B463">
-        <v>54675776</v>
+        <v>65720</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Tetracycline</t>
+          <t>Terizidone</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Antimycobacterials</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>A01AB13,D06AA04,J01AA07,QA01AB13,QD06AA04,QG01AA90,QG51AA02,QJ01AA07,QJ51AA07,QS01AA09,QS02AA08,QS03AA02,S01AA09,S02AA08,S03AA02</t>
+          <t>J04AK03,QJ04AK03</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Drugs for treatment of tuberculosis</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Other drugs for treatment of tuberculosis</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>tc,te,tet,tetcyc,tetr,tetra</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>abramycin,abricycline,agromicina,ambramicina,ambramycin,biocycline,brodspec,cefracycline,centet,ciclibion,copharlan,criseociclina,democracin,deschlorobiomycin,economycin,hostacyclin,lexacycline,limecycline,liquamycin,mericycline,micycline,neocycline,omegamycin,orlycycline,panmycin,purocyclina,roviciclina,solvocin,tetrabon,tetraciclina,tetracyclinehydrate,tetracyclinum,tetracyn,tetradecin,tetrafil,tetraverine,tetrazyklin,tsiklomistsin,tsiklomitsin,veracin,vetacyclinum</t>
-        </is>
-      </c>
-      <c r="J463">
-        <v>1</v>
-      </c>
-      <c r="K463" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L463">
-        <v>1</v>
-      </c>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>terivalidin,terizidona,terizidonum</t>
+        </is>
+      </c>
+      <c r="J463" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K463" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L463" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M463" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t>101504-9,18993-6,25272-6,4045-1,495-2,496-0,497-8,498-6,7052-4,87590-6</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>TCY-S</t>
-        </is>
-      </c>
-      <c r="B464" t="e">
-        <v>#N/A</v>
+          <t>TCY</t>
+        </is>
+      </c>
+      <c r="B464">
+        <v>54675776</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Tetracycline screening test</t>
+          <t>Tetracycline</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -28955,55 +28951,63 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F464" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G464" t="e">
-        <v>#N/A</v>
+          <t>A01AB13,D06AA04,J01AA07,QA01AB13,QD06AA04,QG01AA90,QG51AA02,QJ01AA07,QJ51AA07,QS01AA09,QS02AA08,QS03AA02,S01AA09,S02AA08,S03AA02</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Tetracyclines</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Tetracyclines</t>
+        </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>tcy screen</t>
+          <t>tc,te,tet,tetcyc,tetr,tetra</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J464" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K464" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L464" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M464" t="e">
-        <v>#N/A</v>
+          <t>abramycin,abricycline,agromicina,ambramicina,ambramycin,biocycline,brodspec,cefracycline,centet,ciclibion,copharlan,criseociclina,democracin,deschlorobiomycin,economycin,hostacyclin,lexacycline,limecycline,liquamycin,mericycline,micycline,neocycline,omegamycin,orlycycline,panmycin,purocyclina,roviciclina,solvocin,tetrabon,tetraciclina,tetracyclinehydrate,tetracyclinum,tetracyn,tetradecin,tetrafil,tetraverine,tetrazyklin,tsiklomistsin,tsiklomitsin,veracin,vetacyclinum</t>
+        </is>
+      </c>
+      <c r="J464">
+        <v>1</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L464">
+        <v>1</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>101504-9,18993-6,25272-6,4045-1,495-2,496-0,497-8,498-6,7052-4,87590-6</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>TOL</t>
-        </is>
-      </c>
-      <c r="B465">
-        <v>54691494</v>
+          <t>TCY-S</t>
+        </is>
+      </c>
+      <c r="B465" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Tetracycline/oleandomycin</t>
+          <t>Tetracycline screening test</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -29013,22 +29017,18 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>J01RA08,QJ01RA08</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>Combinations of antibacterials</t>
-        </is>
-      </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>Combinations of antibacterials</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F465" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G465" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tcy screen</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29057,32 +29057,36 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>TET</t>
+          <t>TOL</t>
         </is>
       </c>
       <c r="B466">
-        <v>65450</v>
+        <v>54691494</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Tetroxoprim</t>
+          <t>Tetracycline/oleandomycin</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F466" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G466" t="e">
-        <v>#N/A</v>
+          <t>J01RA08,QJ01RA08</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Combinations of antibacterials</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Combinations of antibacterials</t>
+        </is>
       </c>
       <c r="H466" t="inlineStr">
         <is>
@@ -29091,7 +29095,7 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>primsol,tetroxoprima,tetroxoprime,tetroxoprimum,trimpex,trimplex</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J466" t="e">
@@ -29115,20 +29119,20 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TET</t>
         </is>
       </c>
       <c r="B467">
-        <v>9568512</v>
+        <v>65450</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Thiacetazone</t>
+          <t>Tetroxoprim</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Oxazolidinones</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -29149,7 +29153,7 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>acetanilide,aktivan,ambathizon,amitiozon,antib,benthiozone,benzothiozane,benzothiozon,berkazon,citazone,conteben,diasan,domakol,ilbion,livazone,mivizon,myvizone,neotibil,neustab,novakol,panrone,parazone,seroden,siocarbazone,tebalon,tebecure,tebemar,tebethion,tebethione,tebezon,thiacetone,thiacetozone,thibon,thibone,thioacetazon,thioacetazonum,thioazetazone,thiocarbazil,thiomicid,thionicid,thioparamizon,thioparamizone,thiosemicarbarzone,thiosemicarbazone,thiotebesin,thiotebezin,thiotebicina,thizone,tiacetazon,tibicur,tibion,tibione,tibizan,tibon,tibone,tioacetazon,tioacetazona,tioatsetazon,tiobicina,tiocarone,tiosecolo,tubercazon,tubigal,tubin</t>
+          <t>primsol,tetroxoprima,tetroxoprime,tetroxoprimum,trimpex,trimplex</t>
         </is>
       </c>
       <c r="J467" t="e">
@@ -29166,142 +29170,138 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t>32384-0,54184-7,54204-3</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>THI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="B468">
-        <v>27200</v>
+        <v>9568512</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Thiamphenicol</t>
+          <t>Thiacetazone</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Phenicols</t>
+          <t>Oxazolidinones</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>J01BA02,QJ01BA02,QJ51BA02</t>
-        </is>
-      </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>Amphenicols</t>
-        </is>
-      </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>Amphenicols</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F468" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G468" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>thiaph</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>armai,dextrosulfenidol,dextrosulphenidol,igralin,racefenicol,racefenicolo,racefenicolum,raceophenidol,thiamphenicolum,thiocymetin,thiophenicol,tiamfenicol,tiamfenicolo,urfamycine</t>
-        </is>
-      </c>
-      <c r="J468">
-        <v>1.5</v>
-      </c>
-      <c r="K468" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L468">
-        <v>1.5</v>
-      </c>
-      <c r="M468" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>acetanilide,aktivan,ambathizon,amitiozon,antib,benthiozone,benzothiozane,benzothiozon,berkazon,citazone,conteben,diasan,domakol,ilbion,livazone,mivizon,myvizone,neotibil,neustab,novakol,panrone,parazone,seroden,siocarbazone,tebalon,tebecure,tebemar,tebethion,tebethione,tebezon,thiacetone,thiacetozone,thibon,thibone,thioacetazon,thioacetazonum,thioazetazone,thiocarbazil,thiomicid,thionicid,thioparamizon,thioparamizone,thiosemicarbarzone,thiosemicarbazone,thiotebesin,thiotebezin,thiotebicina,thizone,tiacetazon,tibicur,tibion,tibione,tibizan,tibon,tibone,tioacetazon,tioacetazona,tioatsetazon,tiobicina,tiocarone,tiosecolo,tubercazon,tubigal,tubin</t>
+        </is>
+      </c>
+      <c r="J468" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K468" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L468" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M468" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t>41723-8,41724-6,41725-3,54169-8</t>
+          <t>32384-0,54184-7,54204-3</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>TAT</t>
-        </is>
-      </c>
-      <c r="B469" t="e">
-        <v>#N/A</v>
+          <t>THI</t>
+        </is>
+      </c>
+      <c r="B469">
+        <v>27200</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Thioacetazone</t>
+          <t>Thiamphenicol</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Antimycobacterials</t>
+          <t>Phenicols</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>J04AK07,QJ04AK07</t>
+          <t>J01BA02,QJ01BA02,QJ51BA02</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>Drugs for treatment of tuberculosis</t>
+          <t>Amphenicols</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Other drugs for treatment of tuberculosis</t>
+          <t>Amphenicols</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>thiaph</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J469" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K469" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L469" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M469" t="e">
-        <v>#N/A</v>
+          <t>armai,dextrosulfenidol,dextrosulphenidol,igralin,racefenicol,racefenicolo,racefenicolum,raceophenidol,thiamphenicolum,thiocymetin,thiophenicol,tiamfenicol,tiamfenicolo,urfamycine</t>
+        </is>
+      </c>
+      <c r="J469">
+        <v>1.5</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L469">
+        <v>1.5</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>41723-8,41724-6,41725-3,54169-8</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>THI1</t>
+          <t>TAT</t>
         </is>
       </c>
       <c r="B470" t="e">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Thioacetazone/isoniazid</t>
+          <t>Thioacetazone</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>J04AM04,QJ04AM04</t>
+          <t>J04AK07,QJ04AK07</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Combinations of drugs for treatment of tuberculosis</t>
+          <t>Other drugs for treatment of tuberculosis</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29363,32 +29363,36 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>THS</t>
-        </is>
-      </c>
-      <c r="B471">
-        <v>16129666</v>
+          <t>THI1</t>
+        </is>
+      </c>
+      <c r="B471" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Thiostrepton</t>
+          <t>Thioacetazone/isoniazid</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Peptides</t>
+          <t>Antimycobacterials</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F471" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G471" t="e">
-        <v>#N/A</v>
+          <t>J04AM04,QJ04AM04</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Drugs for treatment of tuberculosis</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Combinations of drugs for treatment of tuberculosis</t>
+        </is>
       </c>
       <c r="H471" t="inlineStr">
         <is>
@@ -29397,7 +29401,7 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>alaninamide,bryamycin,gargon,sporangiomycin,thiactin,tiostrepton</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J471" t="e">
@@ -29421,25 +29425,25 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>TIA</t>
+          <t>THS</t>
         </is>
       </c>
       <c r="B472">
-        <v>656958</v>
+        <v>16129666</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Tiamulin</t>
+          <t>Thiostrepton</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Pleuromutilins</t>
+          <t>Peptides</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>QJ01XQ01</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F472" t="e">
@@ -29450,12 +29454,12 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>tiamul</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>denagard,thiamutilin,tiamulina,tiamuline,tiamulinum</t>
+          <t>alaninamide,bryamycin,gargon,sporangiomycin,thiactin,tiostrepton</t>
         </is>
       </c>
       <c r="J472" t="e">
@@ -29472,52 +29476,48 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t>35846-5,35847-3,35848-1,87589-8</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>TIC</t>
+          <t>TIA</t>
         </is>
       </c>
       <c r="B473">
-        <v>36921</v>
+        <v>656958</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Ticarcillin</t>
+          <t>Tiamulin</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Penicillins,Beta-lactams</t>
+          <t>Pleuromutilins</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>J01CA13,QJ01CA13</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>Beta-lactam antibacterials, penicillins</t>
-        </is>
-      </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>Penicillins with extended spectrum</t>
-        </is>
+          <t>QJ01XQ01</t>
+        </is>
+      </c>
+      <c r="F473" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G473" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>tc,ti,tic,tica,ticarc</t>
+          <t>tiamul</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>ticar,ticarcilina,ticarcilline,ticarcillinum</t>
+          <t>denagard,thiamutilin,tiamulina,tiamuline,tiamulinum</t>
         </is>
       </c>
       <c r="J473" t="e">
@@ -29526,42 +29526,40 @@
       <c r="K473" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L473">
-        <v>15</v>
-      </c>
-      <c r="M473" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+      <c r="L473" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M473" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t>18994-4,18995-1,25254-4,4054-3,4055-0,499-4,500-9,501-7,502-5,503-3,504-1,505-8,506-6,55716-5,55717-3,55718-1,55719-9,7053-2,7054-0</t>
+          <t>35846-5,35847-3,35848-1,87589-8</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>TIC</t>
         </is>
       </c>
       <c r="B474">
-        <v>6437075</v>
+        <v>36921</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Ticarcillin/clavulanic acid</t>
+          <t>Ticarcillin</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Penicillins,Beta-lactams,Beta-lactamase inhibitors</t>
+          <t>Penicillins,Beta-lactams</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>J01CR03,QJ01CR03</t>
+          <t>J01CA13,QJ01CA13</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -29571,17 +29569,17 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Combinations of penicillins, incl. beta-lactamase inhibitors</t>
+          <t>Penicillins with extended spectrum</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>t/c,tcc,ticcla,ticl,tim,tlc</t>
+          <t>tc,ti,tic,tica,ticarc</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>augpenin,timentin</t>
+          <t>ticar,ticarcilina,ticarcilline,ticarcillinum</t>
         </is>
       </c>
       <c r="J474" t="e">
@@ -29600,52 +29598,52 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18994-4,18995-1,25254-4,4054-3,4055-0,499-4,500-9,501-7,502-5,503-3,504-1,505-8,506-6,55716-5,55717-3,55718-1,55719-9,7053-2,7054-0</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>TGC</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B475">
-        <v>54686904</v>
+        <v>6437075</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Tigecycline</t>
+          <t>Ticarcillin/clavulanic acid</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Penicillins,Beta-lactams,Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>J01AA12,QJ01AA12</t>
+          <t>J01CR03,QJ01CR03</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Beta-lactam antibacterials, penicillins</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Combinations of penicillins, incl. beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>tgc,tig,tige,tigecy</t>
+          <t>t/c,tcc,ticcla,ticl,tim,tlc</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>tigeciclina,tigecyclin,tigecyclinehydrate,tigilcycline,tygacil</t>
+          <t>augpenin,timentin</t>
         </is>
       </c>
       <c r="J475" t="e">
@@ -29655,7 +29653,7 @@
         <v>#N/A</v>
       </c>
       <c r="L475">
-        <v>0.1</v>
+        <v>15</v>
       </c>
       <c r="M475" t="inlineStr">
         <is>
@@ -29664,48 +29662,52 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t>101499-2,42354-1,42355-8,42356-6,42357-4,55158-0</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>TMN</t>
-        </is>
-      </c>
-      <c r="B476" t="e">
-        <v>#N/A</v>
+          <t>TGC</t>
+        </is>
+      </c>
+      <c r="B476">
+        <v>54686904</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Tigemonam</t>
+          <t>Tigecycline</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Monobactams,Beta-lactams</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F476" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G476" t="e">
-        <v>#N/A</v>
+          <t>J01AA12,QJ01AA12</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Tetracyclines</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Tetracyclines</t>
+        </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tgc,tig,tige,tigecy</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tigeciclina,tigecyclin,tigecyclinehydrate,tigilcycline,tygacil</t>
         </is>
       </c>
       <c r="J476" t="e">
@@ -29714,40 +29716,42 @@
       <c r="K476" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L476" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M476" t="e">
-        <v>#N/A</v>
+      <c r="L476">
+        <v>0.1</v>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>101499-2,42354-1,42355-8,42356-6,42357-4,55158-0</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>TBQ</t>
-        </is>
-      </c>
-      <c r="B477">
-        <v>65592</v>
+          <t>TMN</t>
+        </is>
+      </c>
+      <c r="B477" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Tilbroquinol</t>
+          <t>Tigemonam</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Fluoroquinolones,Quinolones</t>
+          <t>Monobactams,Beta-lactams</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>P01AA05</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F477" t="e">
@@ -29763,7 +29767,7 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>tilbroquinolum</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J477" t="e">
@@ -29787,25 +29791,25 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>TIP</t>
+          <t>TBQ</t>
         </is>
       </c>
       <c r="B478">
-        <v>24860548</v>
+        <v>65592</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Tildipirosin</t>
+          <t>Tilbroquinol</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Fluoroquinolones,Quinolones</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>QJ01FA96</t>
+          <t>P01AA05</t>
         </is>
       </c>
       <c r="F478" t="e">
@@ -29821,7 +29825,7 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>zuprevo</t>
+          <t>tilbroquinolum</t>
         </is>
       </c>
       <c r="J478" t="e">
@@ -29838,22 +29842,22 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t>100060-3,88375-1,88377-7</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>TIP</t>
         </is>
       </c>
       <c r="B479">
-        <v>5282521</v>
+        <v>24860548</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Tilmicosin</t>
+          <t>Tildipirosin</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29863,7 +29867,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>QJ01FA91</t>
+          <t>QJ01FA96</t>
         </is>
       </c>
       <c r="F479" t="e">
@@ -29874,12 +29878,12 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>tilmic</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>micotil,pulmotil,tilmicosina,tilmicosine,tilmicosinum,tilmovet</t>
+          <t>zuprevo</t>
         </is>
       </c>
       <c r="J479" t="e">
@@ -29896,169 +29900,167 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t>35849-9,35850-7,35851-5,87588-0</t>
+          <t>100060-3,88375-1,88377-7</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>TIN</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B480">
-        <v>5479</v>
+        <v>5282521</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Tinidazole</t>
+          <t>Tilmicosin</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>G01AF21,J01XD02,P01AB02,QG01AF21,QJ01XD02,QP51AA02</t>
-        </is>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
-      </c>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>Imidazole derivatives</t>
-        </is>
+          <t>QJ01FA91</t>
+        </is>
+      </c>
+      <c r="F480" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G480" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>tini</t>
+          <t>tilmic</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>amtiba,bioshik,fasigin,fasigyn,glongyn,haisigyn,isotinidazole,pletil,protozol,simplotan,sorquetan,symplotan,tindamax,tindazole,tinidazolum,tricolam,trimonase</t>
-        </is>
-      </c>
-      <c r="J480">
-        <v>2</v>
-      </c>
-      <c r="K480" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L480">
-        <v>1.5</v>
-      </c>
-      <c r="M480" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>micotil,pulmotil,tilmicosina,tilmicosine,tilmicosinum,tilmovet</t>
+        </is>
+      </c>
+      <c r="J480" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K480" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L480" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M480" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t>54928-7,55720-7,55721-5,55722-3</t>
+          <t>35849-9,35850-7,35851-5,87588-0</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>TCR</t>
+          <t>TIN</t>
         </is>
       </c>
       <c r="B481">
-        <v>3001386</v>
+        <v>5479</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Tiocarlide</t>
+          <t>Tinidazole</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Antimycobacterials</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>J04AD02,QJ04AD02</t>
+          <t>G01AF21,J01XD02,P01AB02,QG01AF21,QJ01XD02,QP51AA02</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Drugs for treatment of tuberculosis</t>
+          <t>Other antibacterials</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Thiocarbamide derivatives</t>
+          <t>Imidazole derivatives</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tini</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>aethoksid,aethoxydum,amixyl,datanil,disocarban,disoxyl,ethoxide,etocarlid,etocarlida,etocarlide,etocarlidum,etoksid,thiocarlide,tiocarlid,tiocarlida,tiocarlidum</t>
+          <t>amtiba,bioshik,fasigin,fasigyn,glongyn,haisigyn,isotinidazole,pletil,protozol,simplotan,sorquetan,symplotan,tindamax,tindazole,tinidazolum,tricolam,trimonase</t>
         </is>
       </c>
       <c r="J481">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="L481" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M481" t="e">
-        <v>#N/A</v>
+      <c r="L481">
+        <v>1.5</v>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>54928-7,55720-7,55721-5,55722-3</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>TDC</t>
+          <t>TCR</t>
         </is>
       </c>
       <c r="B482">
-        <v>10247721</v>
+        <v>3001386</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Tiodonium chloride</t>
+          <t>Tiocarlide</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Antimycobacterials</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F482" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G482" t="e">
-        <v>#N/A</v>
+          <t>J04AD02,QJ04AD02</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Drugs for treatment of tuberculosis</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Thiocarbamide derivatives</t>
+        </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
@@ -30067,14 +30069,16 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>tiodonium</t>
-        </is>
-      </c>
-      <c r="J482" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K482" t="e">
-        <v>#N/A</v>
+          <t>aethoksid,aethoxydum,amixyl,datanil,disocarban,disoxyl,ethoxide,etocarlid,etocarlida,etocarlide,etocarlidum,etoksid,thiocarlide,tiocarlid,tiocarlida,tiocarlidum</t>
+        </is>
+      </c>
+      <c r="J482">
+        <v>7</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L482" t="e">
         <v>#N/A</v>
@@ -30091,20 +30095,20 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>TXC</t>
+          <t>TDC</t>
         </is>
       </c>
       <c r="B483">
-        <v>65788</v>
+        <v>10247721</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Tioxacin</t>
+          <t>Tiodonium chloride</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Fluoroquinolones,Quinolones</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -30125,7 +30129,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>tioxacine,tioxacino,tioxacinum</t>
+          <t>tiodonium</t>
         </is>
       </c>
       <c r="J483" t="e">
@@ -30149,20 +30153,20 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>TIZ</t>
+          <t>TXC</t>
         </is>
       </c>
       <c r="B484">
-        <v>394397</v>
+        <v>65788</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Tizoxanide</t>
+          <t>Tioxacin</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fluoroquinolones,Quinolones</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -30183,7 +30187,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tioxacine,tioxacino,tioxacinum</t>
         </is>
       </c>
       <c r="J484" t="e">
@@ -30200,52 +30204,48 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t>73585-2,73607-4,73629-8</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>TOB</t>
+          <t>TIZ</t>
         </is>
       </c>
       <c r="B485">
-        <v>36294</v>
+        <v>394397</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Tobramycin</t>
+          <t>Tizoxanide</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>J01GB01,QJ01GB01,QS01AA12,S01AA12</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>Aminoglycoside antibacterials</t>
-        </is>
-      </c>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>Other aminoglycosides</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F485" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G485" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>nn,tm,to,tob,tobr,tobram</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>aktob,bethkis,distobram,gotabiotic,kitabis,nebcin,nebicin,nebramycin,tenebrimycin,tenemycin,tobacin,tobracin,tobradex,tobradistin,tobralex,tobramaxin,tobramicin,tobramicina,tobramitsetin,tobramycetin,tobramycine,tobramycinum,tobrased,tobrex</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J485" t="e">
@@ -30254,32 +30254,30 @@
       <c r="K485" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L485">
-        <v>0.24</v>
-      </c>
-      <c r="M485" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+      <c r="L485" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M485" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t>101496-8,13584-8,17808-7,18996-9,22750-4,22751-2,22752-0,25227-0,25800-4,31094-6,31095-3,31096-1,35239-3,35670-9,4057-6,4058-4,4059-2,507-4,508-2,509-0,50927-3,510-8,52962-8,59380-6,7055-7,80966-5</t>
+          <t>73585-2,73607-4,73629-8</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>TOH</t>
-        </is>
-      </c>
-      <c r="B486" t="e">
-        <v>#N/A</v>
+          <t>TOB</t>
+        </is>
+      </c>
+      <c r="B486">
+        <v>36294</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Tobramycin-high</t>
+          <t>Tobramycin</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -30289,23 +30287,27 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F486" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G486" t="e">
-        <v>#N/A</v>
+          <t>J01GB01,QJ01GB01,QS01AA12,S01AA12</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Aminoglycoside antibacterials</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Other aminoglycosides</t>
+        </is>
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>tobra high,tobramycin high,tohl</t>
+          <t>nn,tm,to,tob,tobr,tobram</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>aktob,bethkis,distobram,gotabiotic,kitabis,nebcin,nebicin,nebramycin,tenebrimycin,tenemycin,tobacin,tobracin,tobradex,tobradistin,tobralex,tobramaxin,tobramicin,tobramicina,tobramitsetin,tobramycetin,tobramycine,tobramycinum,tobrased,tobrex</t>
         </is>
       </c>
       <c r="J486" t="e">
@@ -30314,40 +30316,42 @@
       <c r="K486" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L486" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M486" t="e">
-        <v>#N/A</v>
+      <c r="L486">
+        <v>0.24</v>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>101496-8,13584-8,17808-7,18996-9,22750-4,22751-2,22752-0,25227-0,25800-4,31094-6,31095-3,31096-1,35239-3,35670-9,4057-6,4058-4,4059-2,507-4,508-2,509-0,50927-3,510-8,52962-8,59380-6,7055-7,80966-5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>TFX</t>
-        </is>
-      </c>
-      <c r="B487">
-        <v>5517</v>
+          <t>TOH</t>
+        </is>
+      </c>
+      <c r="B487" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Tosufloxacin</t>
+          <t>Tobramycin-high</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Fluoroquinolones,Quinolones</t>
+          <t>Aminoglycosides</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>J01MA22,QJ01MA22,QS01AE09,S01AE09</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F487" t="e">
@@ -30358,7 +30362,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>tosufl</t>
+          <t>tobra high,tobramycin high,tohl</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30366,13 +30370,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J487">
-        <v>0.45</v>
-      </c>
-      <c r="K487" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+      <c r="J487" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K487" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L487" t="e">
         <v>#N/A</v>
@@ -30382,98 +30384,92 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t>100061-1,76146-0</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>TMP</t>
+          <t>TFX</t>
         </is>
       </c>
       <c r="B488">
-        <v>5578</v>
+        <v>5517</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Trimethoprim</t>
+          <t>Tosufloxacin</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Trimethoprims</t>
+          <t>Fluoroquinolones,Quinolones</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>J01EA01,QJ01EA01,QJ51EA01</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>Sulfonamides and trimethoprim</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>Trimethoprim and derivatives</t>
-        </is>
+          <t>J01MA22,QJ01MA22,QS01AE09,S01AE09</t>
+        </is>
+      </c>
+      <c r="F488" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G488" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>t,tmp,tr,tri,trim,w</t>
+          <t>tosufl</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>abaprim,anitrim,antrima,antrimox,bacdan,bacidal,bacide,bacin,bacterial,bacticel,bactifor,bactoprim,bactramin,bencole,bethaprim,biosulten,briscotrim,chemotrin,colizole,conprim,cotrimel,deprim,dosulfin,duocide,esbesul,espectrin,euctrim,exbesul,fermagex,fortrim,futin,ikaprim,infectotrimet,instalac,kombinax,lagatrim,lastrim,lescot,monoprim,monotrim,monotrimin,novotrimel,omstat,pancidim,proloprim,protrin,purbal,resprim,roubac,roubal,salvatrim,setprin,sinotrim,stopan,streptoplus,sugaprim,sulfamar,sulfoxaprim,sulthrim,sultrex,syraprim,tiempe,trimethioprim,trimethoprime,trimethoprimum,trimethopriom,trimetoprim,trimetoprima,trimexol,trimezol,trimogal,trimono,trimopan,triprim,trisul,trisulcom,trisulfam,trisural,uretrim,urobactrim,utetrin,velaten,wellcoprim,wellcoprin,xeroprim,zamboprim</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J488">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K488" t="inlineStr">
         <is>
           <t>g</t>
         </is>
       </c>
-      <c r="L488">
-        <v>0.4</v>
-      </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+      <c r="L488" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M488" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t>101495-0,11005-6,17747-7,18997-7,18998-5,20387-7,23614-1,23631-5,25273-4,32342-8,4079-0,4080-8,4081-6,511-6,512-4,513-2,514-0,515-7,516-5,517-3,518-1,55584-7,7056-5,7057-3,80552-3,80973-1</t>
+          <t>100061-1,76146-0</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>SXT</t>
+          <t>TMP</t>
         </is>
       </c>
       <c r="B489">
-        <v>358641</v>
+        <v>5578</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Trimethoprim/sulfamethoxazole</t>
+          <t>Trimethoprim</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Trimethoprims,Sulfonamides</t>
+          <t>Trimethoprims</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>J01EE01</t>
+          <t>J01EA01,QJ01EA01,QJ51EA01</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -30483,88 +30479,90 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
+          <t>Trimethoprim and derivatives</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>cot,cotrim,sxt,t/s,tms,trisul,trsu,trsx,ts</t>
+          <t>t,tmp,tr,tri,trim,w</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>abacin,abactrim,agoprim,alfatrim,aposulfatrim,bacteral,bactilen,bactiver,bacton,bactoreduct,bactrim,bactrizol,bactromin,bactropin,baktar,benzenesulfonamide,berlocid,bibacrim,biseptol,centran,centrin,chemitrim,chemotrim,ciplin,comox,cotribene,cotrim,cotrimhexal,cotrimoxazol,cotrimoxazole,cotrimstada,cotriver,dibaprim,drylin,duratrimet,eltrianyl,escoprim,eslectin,esteprim,eusaprim,fectrim,gamazole,gantanol,gantaprim,gantaprin,gantrim,groprim,helveprim,imexim,insozalin,jenamoxazol,kemoprim,kepinol,laratrim,linaris,maxtrim,metoxal,microtrim,mikrosid,momentol,nopil,oecotrim,omsat,oriprim,oxaprim,pantoprim,potrox,primazole,radonil,septra,septrim,servitrim,sigaprim,sigaprin,sulfatrim,sulfotrim,sulfotrimin,sulmeprim,sulprim,sumetrolim,supracombin,suprim,tacumil,teleprim,teleprin,thiocuran,tribakin,trifen,trigonyl,trimedin,trimesulf,trimethoprimsulfa,trimetoger,trimexazol,trimezole,trimforte,trimosulfa,uroplus</t>
-        </is>
-      </c>
-      <c r="J489" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K489" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L489" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M489" t="e">
-        <v>#N/A</v>
+          <t>abaprim,anitrim,antrima,antrimox,bacdan,bacidal,bacide,bacin,bacterial,bacticel,bactifor,bactoprim,bactramin,bencole,bethaprim,biosulten,briscotrim,chemotrin,colizole,conprim,cotrimel,deprim,dosulfin,duocide,esbesul,espectrin,euctrim,exbesul,fermagex,fortrim,futin,ikaprim,infectotrimet,instalac,kombinax,lagatrim,lastrim,lescot,monoprim,monotrim,monotrimin,novotrimel,omstat,pancidim,proloprim,protrin,purbal,resprim,roubac,roubal,salvatrim,setprin,sinotrim,stopan,streptoplus,sugaprim,sulfamar,sulfoxaprim,sulthrim,sultrex,syraprim,tiempe,trimethioprim,trimethoprime,trimethoprimum,trimethopriom,trimetoprim,trimetoprima,trimexol,trimezol,trimogal,trimono,trimopan,triprim,trisul,trisulcom,trisulfam,trisural,uretrim,urobactrim,utetrin,velaten,wellcoprim,wellcoprin,xeroprim,zamboprim</t>
+        </is>
+      </c>
+      <c r="J489">
+        <v>0.4</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L489">
+        <v>0.4</v>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t>101495-0,18998-5,20387-7,23631-5,25273-4,32342-8,4081-6,515-7,516-5,517-3,518-1,7057-3</t>
+          <t>101495-0,11005-6,17747-7,18997-7,18998-5,20387-7,23614-1,23631-5,25273-4,32342-8,4079-0,4080-8,4081-6,511-6,512-4,513-2,514-0,515-7,516-5,517-3,518-1,55584-7,7056-5,7057-3,80552-3,80973-1</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>TRL</t>
+          <t>SXT</t>
         </is>
       </c>
       <c r="B490">
-        <v>202225</v>
+        <v>358641</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Troleandomycin</t>
+          <t>Trimethoprim/sulfamethoxazole</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Trimethoprims,Sulfonamides</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>J01FA08,QJ01FA08</t>
+          <t>J01EE01</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Macrolides, lincosamides and streptogramins</t>
+          <t>Sulfonamides and trimethoprim</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Combinations of sulfonamides and trimethoprim, incl. derivatives</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>cot,cotrim,sxt,t/s,tms,trisul,trsu,trsx,ts</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>aovine,cyclamycin,evramicina,matromicina,oleandocetin,oleandocetine,tekmisin,treolmicina,tribiocillina,triocetin,triolan,troleandomicina,troleandomycine,troleandomycinum,viamicina,wytrion</t>
-        </is>
-      </c>
-      <c r="J490">
-        <v>1</v>
-      </c>
-      <c r="K490" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>abacin,abactrim,agoprim,alfatrim,aposulfatrim,bacteral,bactilen,bactiver,bacton,bactoreduct,bactrim,bactrizol,bactromin,bactropin,baktar,benzenesulfonamide,berlocid,bibacrim,biseptol,centran,centrin,chemitrim,chemotrim,ciplin,comox,cotribene,cotrim,cotrimhexal,cotrimoxazol,cotrimoxazole,cotrimstada,cotriver,dibaprim,drylin,duratrimet,eltrianyl,escoprim,eslectin,esteprim,eusaprim,fectrim,gamazole,gantanol,gantaprim,gantaprin,gantrim,groprim,helveprim,imexim,insozalin,jenamoxazol,kemoprim,kepinol,laratrim,linaris,maxtrim,metoxal,microtrim,mikrosid,momentol,nopil,oecotrim,omsat,oriprim,oxaprim,pantoprim,potrox,primazole,radonil,septra,septrim,servitrim,sigaprim,sigaprin,sulfatrim,sulfotrim,sulfotrimin,sulmeprim,sulprim,sumetrolim,supracombin,suprim,tacumil,teleprim,teleprin,thiocuran,tribakin,trifen,trigonyl,trimedin,trimesulf,trimethoprimsulfa,trimetoger,trimexazol,trimezole,trimforte,trimosulfa,uroplus</t>
+        </is>
+      </c>
+      <c r="J490" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K490" t="e">
+        <v>#N/A</v>
       </c>
       <c r="L490" t="e">
         <v>#N/A</v>
@@ -30574,55 +30572,61 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t>18999-3,519-9,520-7,521-5,522-3</t>
+          <t>101495-0,18998-5,20387-7,23631-5,25273-4,32342-8,4081-6,515-7,516-5,517-3,518-1,7057-3</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>TRL</t>
         </is>
       </c>
       <c r="B491">
-        <v>55886</v>
+        <v>202225</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Trospectomycin</t>
+          <t>Troleandomycin</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F491" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G491" t="e">
-        <v>#N/A</v>
+          <t>J01FA08,QJ01FA08</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Macrolides, lincosamides and streptogramins</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Macrolides</t>
+        </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>trospe</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>trospectinomycin,trospectomicina,trospectomycine,trospectomycinum</t>
-        </is>
-      </c>
-      <c r="J491" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K491" t="e">
-        <v>#N/A</v>
+          <t>aovine,cyclamycin,evramicina,matromicina,oleandocetin,oleandocetine,tekmisin,treolmicina,tribiocillina,triocetin,triolan,troleandomicina,troleandomycine,troleandomycinum,viamicina,wytrion</t>
+        </is>
+      </c>
+      <c r="J491">
+        <v>1</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="L491" t="e">
         <v>#N/A</v>
@@ -30632,146 +30636,146 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>18999-3,519-9,520-7,521-5,522-3</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>TVA</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="B492">
-        <v>62959</v>
+        <v>55886</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Trovafloxacin</t>
+          <t>Trospectomycin</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Fluoroquinolones,Quinolones</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>J01MA13,QJ01MA13</t>
-        </is>
-      </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>Quinolone antibacterials</t>
-        </is>
-      </c>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F492" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G492" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>trov,trovaf</t>
+          <t>trospe</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>trovan,turvel</t>
-        </is>
-      </c>
-      <c r="J492">
-        <v>0.2</v>
-      </c>
-      <c r="K492" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L492">
-        <v>0.2</v>
-      </c>
-      <c r="M492" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>trospectinomycin,trospectomicina,trospectomycine,trospectomycinum</t>
+        </is>
+      </c>
+      <c r="J492" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K492" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L492" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M492" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t>23642-2,23643-0,35855-6,7058-1</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>TUL</t>
+          <t>TVA</t>
         </is>
       </c>
       <c r="B493">
-        <v>9832301</v>
+        <v>62959</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Tulathromycin</t>
+          <t>Trovafloxacin</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Fluoroquinolones,Quinolones</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>QJ01FA94</t>
-        </is>
-      </c>
-      <c r="F493" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G493" t="e">
-        <v>#N/A</v>
+          <t>J01MA13,QJ01MA13</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Quinolone antibacterials</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Fluoroquinolones</t>
+        </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>tulath</t>
+          <t>trov,trovaf</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>arovyn,draxxin,increxxa,macrosyn,tulieve,tulissin</t>
-        </is>
-      </c>
-      <c r="J493" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K493" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L493" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M493" t="e">
-        <v>#N/A</v>
+          <t>trovan,turvel</t>
+        </is>
+      </c>
+      <c r="J493">
+        <v>0.2</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L493">
+        <v>0.2</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t>76149-4,87798-5</t>
+          <t>23642-2,23643-0,35855-6,7058-1</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>TUL</t>
         </is>
       </c>
       <c r="B494">
-        <v>5280440</v>
+        <v>9832301</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Tylosin</t>
+          <t>Tulathromycin</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -30781,7 +30785,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>QJ01FA90,QJ51FA90</t>
+          <t>QJ01FA94</t>
         </is>
       </c>
       <c r="F494" t="e">
@@ -30792,12 +30796,12 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>tylo</t>
+          <t>tulath</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>fradizine,tilosina,tylan,tylocine,tylosine,tylosinum,vubityl</t>
+          <t>arovyn,draxxin,increxxa,macrosyn,tulieve,tulissin</t>
         </is>
       </c>
       <c r="J494" t="e">
@@ -30814,22 +30818,22 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t>35856-4,35857-2,35858-0,87587-2</t>
+          <t>76149-4,87798-5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>TYL1</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B495">
-        <v>6441094</v>
+        <v>5280440</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Tylvalosin</t>
+          <t>Tylosin</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -30839,7 +30843,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>QJ01FA92</t>
+          <t>QJ01FA90,QJ51FA90</t>
         </is>
       </c>
       <c r="F495" t="e">
@@ -30850,12 +30854,12 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>tvn</t>
+          <t>tylo</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>aivlosin</t>
+          <t>fradizine,tilosina,tylan,tylocine,tylosine,tylosinum,vubityl</t>
         </is>
       </c>
       <c r="J495" t="e">
@@ -30872,32 +30876,32 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t>101526-2,87586-4</t>
+          <t>35856-4,35857-2,35858-0,87587-2</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>PRU1</t>
+          <t>TYL1</t>
         </is>
       </c>
       <c r="B496">
-        <v>124225</v>
+        <v>6441094</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Ulifloxacin (Prulifloxacin)</t>
+          <t>Tylvalosin</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>QJ01FA92</t>
         </is>
       </c>
       <c r="F496" t="e">
@@ -30908,12 +30912,12 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>tvn</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>aivlosin</t>
         </is>
       </c>
       <c r="J496" t="e">
@@ -30930,88 +30934,80 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>101526-2,87586-4</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>PRU1</t>
         </is>
       </c>
       <c r="B497">
-        <v>14969</v>
+        <v>124225</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Vancomycin</t>
+          <t>Ulifloxacin (Prulifloxacin)</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Glycopeptides,Peptides</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>A07AA09,J01XA01,QA07AA09,QJ01XA01,QS01AA28,S01AA28</t>
-        </is>
-      </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>Glycopeptide antibacterials</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F497" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G497" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>va,van,vanc,vancom</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>vancocin,vancoled,vancomicina,vancomycine,vancomycinum</t>
-        </is>
-      </c>
-      <c r="J497">
-        <v>2</v>
-      </c>
-      <c r="K497" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L497">
-        <v>2</v>
-      </c>
-      <c r="M497" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J497" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K497" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L497" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M497" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N497" t="inlineStr">
         <is>
-          <t>13586-3,13587-1,19000-9,20578-1,23615-8,25228-8,31012-8,39092-2,39796-8,39797-6,4089-9,4090-7,4091-5,4092-3,50938-0,523-1,524-9,525-6,526-4,59381-4,7059-9,92241-9,97657-1</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>VAM</t>
-        </is>
-      </c>
-      <c r="B498" t="e">
-        <v>#N/A</v>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="B498">
+        <v>14969</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Vancomycin-macromethod</t>
+          <t>Vancomycin</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -31021,60 +31017,68 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F498" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G498" t="e">
-        <v>#N/A</v>
+          <t>A07AA09,J01XA01,QA07AA09,QJ01XA01,QS01AA28,S01AA28</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Other antibacterials</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Glycopeptide antibacterials</t>
+        </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>va,van,vanc,vancom</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J498" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K498" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L498" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M498" t="e">
-        <v>#N/A</v>
+          <t>vancocin,vancoled,vancomicina,vancomycine,vancomycinum</t>
+        </is>
+      </c>
+      <c r="J498">
+        <v>2</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L498">
+        <v>2</v>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N498" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13586-3,13587-1,19000-9,20578-1,23615-8,25228-8,31012-8,39092-2,39796-8,39797-6,4089-9,4090-7,4091-5,4092-3,50938-0,523-1,524-9,525-6,526-4,59381-4,7059-9,92241-9,97657-1</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>VIO</t>
-        </is>
-      </c>
-      <c r="B499">
-        <v>135398671</v>
+          <t>VAM</t>
+        </is>
+      </c>
+      <c r="B499" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Viomycin</t>
+          <t>Vancomycin-macromethod</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Antimycobacterials</t>
+          <t>Glycopeptides,Peptides</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -31095,7 +31099,7 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>florimycin,floromycin,vioactane,viocin,viomicin,viomicina,viomycine,viomycinum</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="J499" t="e">
@@ -31112,27 +31116,27 @@
       </c>
       <c r="N499" t="inlineStr">
         <is>
-          <t>19001-7,23616-6,527-2,528-0,529-8,530-6</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>VIR</t>
-        </is>
-      </c>
-      <c r="B500" t="e">
-        <v>#N/A</v>
+          <t>VIO</t>
+        </is>
+      </c>
+      <c r="B500">
+        <v>135398671</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Virginiamycine</t>
+          <t>Viomycin</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Streptogramins</t>
+          <t>Antimycobacterials</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -31153,7 +31157,7 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>florimycin,floromycin,vioactane,viocin,viomicin,viomicina,viomycine,viomycinum</t>
         </is>
       </c>
       <c r="J500" t="e">
@@ -31170,167 +31174,163 @@
       </c>
       <c r="N500" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19001-7,23616-6,527-2,528-0,529-8,530-6</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>VOR</t>
-        </is>
-      </c>
-      <c r="B501">
-        <v>71616</v>
+          <t>VIR</t>
+        </is>
+      </c>
+      <c r="B501" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Voriconazole</t>
+          <t>Virginiamycine</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Antifungals</t>
+          <t>Streptogramins</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>J02AC03,QJ02AC03</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>Antimycotics for systemic use</t>
-        </is>
-      </c>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>Triazole derivatives</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F501" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G501" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>vori,vorico,vrc</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>vfend,voriconazol,voriconazolum,voriconzole,vorikonazole</t>
-        </is>
-      </c>
-      <c r="J501">
-        <v>0.4</v>
-      </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="L501">
-        <v>0.4</v>
-      </c>
-      <c r="M501" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="J501" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K501" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L501" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M501" t="e">
+        <v>#N/A</v>
       </c>
       <c r="N501" t="inlineStr">
         <is>
-          <t>32379-0,35862-2,35863-0,38370-3,41199-1,41200-7,53902-3,73676-9,80553-1,80651-3</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>XER</t>
+          <t>VOR</t>
         </is>
       </c>
       <c r="B502">
-        <v>140830474</v>
+        <v>71616</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Xeruborbactam</t>
+          <t>Voriconazole</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Beta-lactamase inhibitors</t>
+          <t>Antifungals</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G502" t="e">
-        <v>#N/A</v>
+          <t>J02AC03,QJ02AC03</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Antimycotics for systemic use</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Triazole derivatives</t>
+        </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>vori,vorico,vrc</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>benzo,borate</t>
-        </is>
-      </c>
-      <c r="J502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L502" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M502" t="e">
-        <v>#N/A</v>
+          <t>vfend,voriconazol,voriconazolum,voriconzole,vorikonazole</t>
+        </is>
+      </c>
+      <c r="J502">
+        <v>0.4</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="L502">
+        <v>0.4</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
       </c>
       <c r="N502" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32379-0,35862-2,35863-0,38370-3,41199-1,41200-7,53902-3,73676-9,80553-1,80651-3</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>XBR</t>
+          <t>XER</t>
         </is>
       </c>
       <c r="B503">
-        <v>72144</v>
+        <v>140830474</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Xibornol</t>
+          <t>Xeruborbactam</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>J01XX02,QJ01XX02</t>
-        </is>
-      </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
-      </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>Other antibacterials</t>
-        </is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F503" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G503" t="e">
+        <v>#N/A</v>
       </c>
       <c r="H503" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>bactacine,bracen,nanbacine,xibornolo,xibornolum</t>
+          <t>benzo,borate</t>
         </is>
       </c>
       <c r="J503" t="e">
@@ -31363,32 +31363,36 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ZID</t>
+          <t>XBR</t>
         </is>
       </c>
       <c r="B504">
-        <v>77846445</v>
+        <v>72144</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Zidebactam</t>
+          <t>Xibornol</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Beta-lactamase inhibitors</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F504" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G504" t="e">
-        <v>#N/A</v>
+          <t>J01XX02,QJ01XX02</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Other antibacterials</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>Other antibacterials</t>
+        </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
@@ -31397,7 +31401,7 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>zidebactamsalt</t>
+          <t>bactacine,bracen,nanbacine,xibornolo,xibornolum</t>
         </is>
       </c>
       <c r="J504" t="e">
@@ -31421,20 +31425,20 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>ZFD</t>
+          <t>ZID</t>
         </is>
       </c>
       <c r="B505">
-        <v>76685216</v>
+        <v>77846445</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Zoliflodacin</t>
+          <t>Zidebactam</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Spiropyrimidinetriones</t>
+          <t>Beta-lactamase inhibitors</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -31450,12 +31454,12 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>zol</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>nuzolvence,zoliflodacina,zoliflodacine</t>
+          <t>zidebactamsalt</t>
         </is>
       </c>
       <c r="J505" t="e">
@@ -31479,56 +31483,114 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
+          <t>ZFD</t>
+        </is>
+      </c>
+      <c r="B506">
+        <v>76685216</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Zoliflodacin</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Spiropyrimidinetriones</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F506" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G506" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>zol</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>nuzolvence,zoliflodacina,zoliflodacine</t>
+        </is>
+      </c>
+      <c r="J506" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K506" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L506" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M506" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
           <t>ZOR</t>
         </is>
       </c>
-      <c r="B506">
+      <c r="B507">
         <v>70697970</v>
       </c>
-      <c r="C506" t="inlineStr">
+      <c r="C507" t="inlineStr">
         <is>
           <t>Zorbamycin</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr">
+      <c r="D507" t="inlineStr">
         <is>
           <t>Glycopeptides,Peptides</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F506" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G506" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="I506" t="inlineStr">
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F507" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G507" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
         <is>
           <t>bleomycetin,boanmycin,pingyangmycin</t>
         </is>
       </c>
-      <c r="J506" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K506" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L506" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M506" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N506" t="inlineStr">
+      <c r="J507" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K507" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L507" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M507" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N507" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
